--- a/data/nzd0317/nzd0317.xlsx
+++ b/data/nzd0317/nzd0317.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P509"/>
+  <dimension ref="A1:P510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27872,7 +27872,7 @@
         <v>397.6</v>
       </c>
       <c r="F509" t="n">
-        <v>402.22</v>
+        <v>399.46</v>
       </c>
       <c r="G509" t="n">
         <v>398.13</v>
@@ -27899,11 +27899,65 @@
         <v>395.1</v>
       </c>
       <c r="O509" t="n">
-        <v>396.76</v>
+        <v>395.2</v>
       </c>
       <c r="P509" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:19:27+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>436.21</v>
+      </c>
+      <c r="C510" t="n">
+        <v>439.14</v>
+      </c>
+      <c r="D510" t="n">
+        <v>410.25</v>
+      </c>
+      <c r="E510" t="n">
+        <v>396.21</v>
+      </c>
+      <c r="F510" t="n">
+        <v>397.67</v>
+      </c>
+      <c r="G510" t="n">
+        <v>396.59</v>
+      </c>
+      <c r="H510" t="n">
+        <v>394.94</v>
+      </c>
+      <c r="I510" t="n">
+        <v>391.52</v>
+      </c>
+      <c r="J510" t="n">
+        <v>389.85</v>
+      </c>
+      <c r="K510" t="n">
+        <v>389.07</v>
+      </c>
+      <c r="L510" t="n">
+        <v>386.14</v>
+      </c>
+      <c r="M510" t="n">
+        <v>385.46</v>
+      </c>
+      <c r="N510" t="n">
+        <v>395.46</v>
+      </c>
+      <c r="O510" t="n">
+        <v>395.94</v>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27918,7 +27972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B534"/>
+  <dimension ref="A1:B535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33261,6 +33315,16 @@
       </c>
       <c r="B534" t="n">
         <v>-1.02</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>
@@ -33429,28 +33493,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>1.555274344797058</v>
+        <v>1.552241957316543</v>
       </c>
       <c r="J2" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K2" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3454785297626235</v>
+        <v>0.3452924245221716</v>
       </c>
       <c r="M2" t="n">
-        <v>11.40009595107732</v>
+        <v>11.39352848475666</v>
       </c>
       <c r="N2" t="n">
-        <v>235.9264638412781</v>
+        <v>235.5914005530481</v>
       </c>
       <c r="O2" t="n">
-        <v>15.35989791116068</v>
+        <v>15.34898695526998</v>
       </c>
       <c r="P2" t="n">
-        <v>403.4863063758213</v>
+        <v>403.5204257994659</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33507,28 +33571,28 @@
         <v>0.0436</v>
       </c>
       <c r="I3" t="n">
-        <v>1.016731290561262</v>
+        <v>1.027872757207779</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K3" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1695639074760552</v>
+        <v>0.1722175293855539</v>
       </c>
       <c r="M3" t="n">
-        <v>13.68042564636655</v>
+        <v>13.72311976852984</v>
       </c>
       <c r="N3" t="n">
-        <v>258.9914372960901</v>
+        <v>260.2219274535698</v>
       </c>
       <c r="O3" t="n">
-        <v>16.09321090696602</v>
+        <v>16.13139570693031</v>
       </c>
       <c r="P3" t="n">
-        <v>382.6275379166423</v>
+        <v>382.501735041092</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33585,28 +33649,28 @@
         <v>0.0762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07044697773164817</v>
+        <v>0.07900981000821608</v>
       </c>
       <c r="J4" t="n">
+        <v>509</v>
+      </c>
+      <c r="K4" t="n">
         <v>508</v>
       </c>
-      <c r="K4" t="n">
-        <v>507</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.002931143518788759</v>
+        <v>0.00365424588569252</v>
       </c>
       <c r="M4" t="n">
-        <v>7.47701008769419</v>
+        <v>7.519088687955143</v>
       </c>
       <c r="N4" t="n">
-        <v>86.25574889527255</v>
+        <v>87.11220641759384</v>
       </c>
       <c r="O4" t="n">
-        <v>9.287397315463172</v>
+        <v>9.333392010281891</v>
       </c>
       <c r="P4" t="n">
-        <v>385.5062331383918</v>
+        <v>385.4095270284936</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33663,28 +33727,28 @@
         <v>0.0934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3598314623785566</v>
+        <v>-0.353967658740035</v>
       </c>
       <c r="J5" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K5" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1075935852951743</v>
+        <v>0.1040007433837928</v>
       </c>
       <c r="M5" t="n">
-        <v>5.872401579603293</v>
+        <v>5.899413972387859</v>
       </c>
       <c r="N5" t="n">
-        <v>54.84153383076579</v>
+        <v>55.21495667400912</v>
       </c>
       <c r="O5" t="n">
-        <v>7.405506993499215</v>
+        <v>7.430676730554837</v>
       </c>
       <c r="P5" t="n">
-        <v>390.0081319387237</v>
+        <v>389.94180945137</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33741,28 +33805,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4308379953752412</v>
+        <v>-0.4249410761578162</v>
       </c>
       <c r="J6" t="n">
+        <v>509</v>
+      </c>
+      <c r="K6" t="n">
         <v>508</v>
       </c>
-      <c r="K6" t="n">
-        <v>507</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.1218691668707345</v>
+        <v>0.1186635421412984</v>
       </c>
       <c r="M6" t="n">
-        <v>6.175486791364041</v>
+        <v>6.20699356254746</v>
       </c>
       <c r="N6" t="n">
-        <v>68.33900128371525</v>
+        <v>68.64146211927995</v>
       </c>
       <c r="O6" t="n">
-        <v>8.266740668710689</v>
+        <v>8.285014310143342</v>
       </c>
       <c r="P6" t="n">
-        <v>390.4686475646444</v>
+        <v>390.4020372517127</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33819,28 +33883,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4203010834857217</v>
+        <v>-0.4133752860469224</v>
       </c>
       <c r="J7" t="n">
+        <v>509</v>
+      </c>
+      <c r="K7" t="n">
         <v>508</v>
       </c>
-      <c r="K7" t="n">
-        <v>507</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1222923716049686</v>
+        <v>0.1180725717794204</v>
       </c>
       <c r="M7" t="n">
-        <v>6.046048366186619</v>
+        <v>6.081324676620316</v>
       </c>
       <c r="N7" t="n">
-        <v>64.78086983298149</v>
+        <v>65.32471365893426</v>
       </c>
       <c r="O7" t="n">
-        <v>8.048656399237172</v>
+        <v>8.082370546995124</v>
       </c>
       <c r="P7" t="n">
-        <v>389.1120536169551</v>
+        <v>389.0338356971574</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33897,28 +33961,28 @@
         <v>0.0761</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4364197725224587</v>
+        <v>-0.4309198466183351</v>
       </c>
       <c r="J8" t="n">
+        <v>509</v>
+      </c>
+      <c r="K8" t="n">
         <v>508</v>
       </c>
-      <c r="K8" t="n">
-        <v>507</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1259592667000176</v>
+        <v>0.1229112374669584</v>
       </c>
       <c r="M8" t="n">
-        <v>6.354901690340693</v>
+        <v>6.380279994501225</v>
       </c>
       <c r="N8" t="n">
-        <v>67.528272009573</v>
+        <v>67.81872488357645</v>
       </c>
       <c r="O8" t="n">
-        <v>8.217558762161241</v>
+        <v>8.235212497779061</v>
       </c>
       <c r="P8" t="n">
-        <v>391.7019776535674</v>
+        <v>391.6398631076161</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33975,28 +34039,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5366147743617843</v>
+        <v>-0.5323802455807021</v>
       </c>
       <c r="J9" t="n">
+        <v>509</v>
+      </c>
+      <c r="K9" t="n">
         <v>508</v>
       </c>
-      <c r="K9" t="n">
-        <v>507</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1697254260836201</v>
+        <v>0.1675268608138782</v>
       </c>
       <c r="M9" t="n">
-        <v>6.340489423195818</v>
+        <v>6.35527962340116</v>
       </c>
       <c r="N9" t="n">
-        <v>71.97394913397243</v>
+        <v>72.08324254533456</v>
       </c>
       <c r="O9" t="n">
-        <v>8.483746173358348</v>
+        <v>8.490185071324097</v>
       </c>
       <c r="P9" t="n">
-        <v>394.2966520579268</v>
+        <v>394.248828535003</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34053,28 +34117,28 @@
         <v>0.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5803193053614262</v>
+        <v>-0.5756161344305664</v>
       </c>
       <c r="J10" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K10" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L10" t="n">
-        <v>0.173722251332136</v>
+        <v>0.1713785300468257</v>
       </c>
       <c r="M10" t="n">
-        <v>6.772498695638504</v>
+        <v>6.787901747835513</v>
       </c>
       <c r="N10" t="n">
-        <v>81.8663872072549</v>
+        <v>82.01491128217786</v>
       </c>
       <c r="O10" t="n">
-        <v>9.048004598100894</v>
+        <v>9.05620843853419</v>
       </c>
       <c r="P10" t="n">
-        <v>392.5253159629032</v>
+        <v>392.4721786199528</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34131,28 +34195,28 @@
         <v>0.0771</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6182296626666961</v>
+        <v>-0.6122864727792405</v>
       </c>
       <c r="J11" t="n">
+        <v>509</v>
+      </c>
+      <c r="K11" t="n">
         <v>508</v>
       </c>
-      <c r="K11" t="n">
-        <v>507</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.1736980318616075</v>
+        <v>0.1707063712519027</v>
       </c>
       <c r="M11" t="n">
-        <v>7.335950820255397</v>
+        <v>7.36410524691675</v>
       </c>
       <c r="N11" t="n">
-        <v>92.900663839619</v>
+        <v>93.21216577336295</v>
       </c>
       <c r="O11" t="n">
-        <v>9.638499044956067</v>
+        <v>9.654644777171399</v>
       </c>
       <c r="P11" t="n">
-        <v>389.4277078326977</v>
+        <v>389.3605871936568</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34209,28 +34273,28 @@
         <v>0.0854</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.501743428057661</v>
+        <v>-0.4962742490895442</v>
       </c>
       <c r="J12" t="n">
+        <v>509</v>
+      </c>
+      <c r="K12" t="n">
         <v>508</v>
       </c>
-      <c r="K12" t="n">
-        <v>507</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.1569280939845541</v>
+        <v>0.1537369807315061</v>
       </c>
       <c r="M12" t="n">
-        <v>6.482448281997634</v>
+        <v>6.510306861788608</v>
       </c>
       <c r="N12" t="n">
-        <v>69.10389920652182</v>
+        <v>69.38652990543768</v>
       </c>
       <c r="O12" t="n">
-        <v>8.312875507700198</v>
+        <v>8.329857736206405</v>
       </c>
       <c r="P12" t="n">
-        <v>384.7015301023221</v>
+        <v>384.6397628032252</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34287,28 +34351,28 @@
         <v>0.102</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1226971419836185</v>
+        <v>-0.1192652877621302</v>
       </c>
       <c r="J13" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K13" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01759252526937427</v>
+        <v>0.01663487827696331</v>
       </c>
       <c r="M13" t="n">
-        <v>4.907887903058016</v>
+        <v>4.923207428898115</v>
       </c>
       <c r="N13" t="n">
-        <v>43.26164813615513</v>
+        <v>43.34315696061026</v>
       </c>
       <c r="O13" t="n">
-        <v>6.577358750756654</v>
+        <v>6.583552001815605</v>
       </c>
       <c r="P13" t="n">
-        <v>379.4558854863834</v>
+        <v>379.417303689662</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34365,28 +34429,28 @@
         <v>0.0586</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.03470001327304053</v>
+        <v>-0.029875610549402</v>
       </c>
       <c r="J14" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K14" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001221621760088665</v>
+        <v>0.0009032602538784351</v>
       </c>
       <c r="M14" t="n">
-        <v>5.23856289661169</v>
+        <v>5.262482938759643</v>
       </c>
       <c r="N14" t="n">
-        <v>50.65966884640828</v>
+        <v>50.88918163628453</v>
       </c>
       <c r="O14" t="n">
-        <v>7.117560596609507</v>
+        <v>7.133665371762579</v>
       </c>
       <c r="P14" t="n">
-        <v>383.3921405021247</v>
+        <v>383.337903313371</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34443,28 +34507,28 @@
         <v>0.0416</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.04961515763124526</v>
+        <v>-0.04830447437007934</v>
       </c>
       <c r="J15" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K15" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003800038848704501</v>
+        <v>0.003613652199463413</v>
       </c>
       <c r="M15" t="n">
-        <v>4.568284992400044</v>
+        <v>4.566137509457621</v>
       </c>
       <c r="N15" t="n">
-        <v>33.08109787626522</v>
+        <v>33.03483153931077</v>
       </c>
       <c r="O15" t="n">
-        <v>5.751616979273326</v>
+        <v>5.747593543328439</v>
       </c>
       <c r="P15" t="n">
-        <v>392.1871726331786</v>
+        <v>392.172378588481</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34502,7 +34566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P509"/>
+  <dimension ref="A1:P510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76113,7 +76177,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>-40.72605026177724,172.3173335818636</t>
+          <t>-40.7260663644119,172.31735848271666</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
@@ -76158,12 +76222,94 @@
       </c>
       <c r="O509" t="inlineStr">
         <is>
-          <t>-40.721295810857704,172.32246689623133</t>
+          <t>-40.72130560461174,172.32248014250845</t>
         </is>
       </c>
       <c r="P509" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:19:27+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-40.72788047797641,172.31466459707704</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-40.72735247959028,172.31523304188107</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-40.72701510033857,172.31608288149124</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-40.72658875436432,172.3168013968382</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-40.72607680778442,172.31737463218937</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-40.72556029268268,172.31793869877444</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-40.725038044358335,172.3185136386369</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-40.72452523934,172.3191054814626</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>-40.72400452569162,172.31967912898116</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>-40.723472589926295,172.3202343129456</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>-40.72295047774018,172.32081143236587</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>-40.72241585238526,172.3213675886238</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>-40.72180550597122,172.3218417710949</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>-40.72130095885681,172.32247385901755</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0317/nzd0317.xlsx
+++ b/data/nzd0317/nzd0317.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P510"/>
+  <dimension ref="A1:P512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27961,6 +27961,114 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>434.53</v>
+      </c>
+      <c r="C511" t="n">
+        <v>436.18</v>
+      </c>
+      <c r="D511" t="n">
+        <v>406.48</v>
+      </c>
+      <c r="E511" t="n">
+        <v>393.18</v>
+      </c>
+      <c r="F511" t="n">
+        <v>394.29</v>
+      </c>
+      <c r="G511" t="n">
+        <v>393.39</v>
+      </c>
+      <c r="H511" t="n">
+        <v>392.06</v>
+      </c>
+      <c r="I511" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="J511" t="n">
+        <v>385.43</v>
+      </c>
+      <c r="K511" t="n">
+        <v>383.66</v>
+      </c>
+      <c r="L511" t="n">
+        <v>381.89</v>
+      </c>
+      <c r="M511" t="n">
+        <v>387.72</v>
+      </c>
+      <c r="N511" t="n">
+        <v>394.1</v>
+      </c>
+      <c r="O511" t="n">
+        <v>395.64</v>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>434.8</v>
+      </c>
+      <c r="C512" t="n">
+        <v>435.23</v>
+      </c>
+      <c r="D512" t="n">
+        <v>403.92</v>
+      </c>
+      <c r="E512" t="n">
+        <v>390.79</v>
+      </c>
+      <c r="F512" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="G512" t="n">
+        <v>390.77</v>
+      </c>
+      <c r="H512" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="I512" t="n">
+        <v>386.75</v>
+      </c>
+      <c r="J512" t="n">
+        <v>382.82</v>
+      </c>
+      <c r="K512" t="n">
+        <v>380.79</v>
+      </c>
+      <c r="L512" t="n">
+        <v>380.2</v>
+      </c>
+      <c r="M512" t="n">
+        <v>386.87</v>
+      </c>
+      <c r="N512" t="n">
+        <v>391.58</v>
+      </c>
+      <c r="O512" t="n">
+        <v>394.2</v>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27972,7 +28080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B535"/>
+  <dimension ref="A1:B537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33325,6 +33433,26 @@
       </c>
       <c r="B535" t="n">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -33493,28 +33621,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>1.552241957316543</v>
+        <v>1.544999543481225</v>
       </c>
       <c r="J2" t="n">
+        <v>511</v>
+      </c>
+      <c r="K2" t="n">
         <v>509</v>
       </c>
-      <c r="K2" t="n">
-        <v>507</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.3452924245221716</v>
+        <v>0.3444715193984792</v>
       </c>
       <c r="M2" t="n">
-        <v>11.39352848475666</v>
+        <v>11.38691037514766</v>
       </c>
       <c r="N2" t="n">
-        <v>235.5914005530481</v>
+        <v>235.0362853279478</v>
       </c>
       <c r="O2" t="n">
-        <v>15.34898695526998</v>
+        <v>15.33089316797778</v>
       </c>
       <c r="P2" t="n">
-        <v>403.5204257994659</v>
+        <v>403.6022147094378</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33571,28 +33699,28 @@
         <v>0.0436</v>
       </c>
       <c r="I3" t="n">
-        <v>1.027872757207779</v>
+        <v>1.04733389703666</v>
       </c>
       <c r="J3" t="n">
+        <v>511</v>
+      </c>
+      <c r="K3" t="n">
         <v>509</v>
       </c>
-      <c r="K3" t="n">
-        <v>507</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1722175293855539</v>
+        <v>0.1772155328406769</v>
       </c>
       <c r="M3" t="n">
-        <v>13.72311976852984</v>
+        <v>13.79100798670189</v>
       </c>
       <c r="N3" t="n">
-        <v>260.2219274535698</v>
+        <v>261.8495750410178</v>
       </c>
       <c r="O3" t="n">
-        <v>16.13139570693031</v>
+        <v>16.18176674658913</v>
       </c>
       <c r="P3" t="n">
-        <v>382.501735041092</v>
+        <v>382.2811897224232</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33649,28 +33777,28 @@
         <v>0.0762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07900981000821608</v>
+        <v>0.09221146724080481</v>
       </c>
       <c r="J4" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K4" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00365424588569252</v>
+        <v>0.004938004238803084</v>
       </c>
       <c r="M4" t="n">
-        <v>7.519088687955143</v>
+        <v>7.57671796473536</v>
       </c>
       <c r="N4" t="n">
-        <v>87.11220641759384</v>
+        <v>87.99354472088342</v>
       </c>
       <c r="O4" t="n">
-        <v>9.333392010281891</v>
+        <v>9.380487445803839</v>
       </c>
       <c r="P4" t="n">
-        <v>385.4095270284936</v>
+        <v>385.2598934306466</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33727,28 +33855,28 @@
         <v>0.0934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.353967658740035</v>
+        <v>-0.345477899233979</v>
       </c>
       <c r="J5" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K5" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1040007433837928</v>
+        <v>0.09939249011327866</v>
       </c>
       <c r="M5" t="n">
-        <v>5.899413972387859</v>
+        <v>5.931986485781385</v>
       </c>
       <c r="N5" t="n">
-        <v>55.21495667400912</v>
+        <v>55.50683458252881</v>
       </c>
       <c r="O5" t="n">
-        <v>7.430676730554837</v>
+        <v>7.450290905899501</v>
       </c>
       <c r="P5" t="n">
-        <v>389.94180945137</v>
+        <v>389.8454398435692</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33805,28 +33933,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4249410761578162</v>
+        <v>-0.4147348181613578</v>
       </c>
       <c r="J6" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K6" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1186635421412984</v>
+        <v>0.1133341829112804</v>
       </c>
       <c r="M6" t="n">
-        <v>6.20699356254746</v>
+        <v>6.258521918079136</v>
       </c>
       <c r="N6" t="n">
-        <v>68.64146211927995</v>
+        <v>69.10704279546765</v>
       </c>
       <c r="O6" t="n">
-        <v>8.285014310143342</v>
+        <v>8.313064585065344</v>
       </c>
       <c r="P6" t="n">
-        <v>390.4020372517127</v>
+        <v>390.2863566467207</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33883,28 +34011,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4133752860469224</v>
+        <v>-0.4029836287503091</v>
       </c>
       <c r="J7" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K7" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1180725717794204</v>
+        <v>0.1124437747107067</v>
       </c>
       <c r="M7" t="n">
-        <v>6.081324676620316</v>
+        <v>6.127631760343026</v>
       </c>
       <c r="N7" t="n">
-        <v>65.32471365893426</v>
+        <v>65.82904150198966</v>
       </c>
       <c r="O7" t="n">
-        <v>8.082370546995124</v>
+        <v>8.113509814007109</v>
       </c>
       <c r="P7" t="n">
-        <v>389.0338356971574</v>
+        <v>388.9160532373857</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33961,28 +34089,28 @@
         <v>0.0761</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4309198466183351</v>
+        <v>-0.4231502851470579</v>
       </c>
       <c r="J8" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K8" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1229112374669584</v>
+        <v>0.1191474925318584</v>
       </c>
       <c r="M8" t="n">
-        <v>6.380279994501225</v>
+        <v>6.408582856899993</v>
       </c>
       <c r="N8" t="n">
-        <v>67.81872488357645</v>
+        <v>67.98135719572741</v>
       </c>
       <c r="O8" t="n">
-        <v>8.235212497779061</v>
+        <v>8.245080787701683</v>
       </c>
       <c r="P8" t="n">
-        <v>391.6398631076161</v>
+        <v>391.5518019913379</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34039,28 +34167,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5323802455807021</v>
+        <v>-0.5268239617218285</v>
       </c>
       <c r="J9" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K9" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1675268608138782</v>
+        <v>0.1652115347500653</v>
       </c>
       <c r="M9" t="n">
-        <v>6.35527962340116</v>
+        <v>6.365977252850501</v>
       </c>
       <c r="N9" t="n">
-        <v>72.08324254533456</v>
+        <v>72.01938040318994</v>
       </c>
       <c r="O9" t="n">
-        <v>8.490185071324097</v>
+        <v>8.48642329860996</v>
       </c>
       <c r="P9" t="n">
-        <v>394.248828535003</v>
+        <v>394.1858527468613</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34117,28 +34245,28 @@
         <v>0.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5756161344305664</v>
+        <v>-0.5705277464740909</v>
       </c>
       <c r="J10" t="n">
+        <v>511</v>
+      </c>
+      <c r="K10" t="n">
         <v>509</v>
       </c>
-      <c r="K10" t="n">
-        <v>507</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1713785300468257</v>
+        <v>0.1695785557345795</v>
       </c>
       <c r="M10" t="n">
-        <v>6.787901747835513</v>
+        <v>6.792197087953901</v>
       </c>
       <c r="N10" t="n">
-        <v>82.01491128217786</v>
+        <v>81.88029772774156</v>
       </c>
       <c r="O10" t="n">
-        <v>9.05620843853419</v>
+        <v>9.048773271982316</v>
       </c>
       <c r="P10" t="n">
-        <v>392.4721786199528</v>
+        <v>392.4144846173681</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34195,28 +34323,28 @@
         <v>0.0771</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6122864727792405</v>
+        <v>-0.6055788684054152</v>
       </c>
       <c r="J11" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K11" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1707063712519027</v>
+        <v>0.1681505279191686</v>
       </c>
       <c r="M11" t="n">
-        <v>7.36410524691675</v>
+        <v>7.383007785817722</v>
       </c>
       <c r="N11" t="n">
-        <v>93.21216577336295</v>
+        <v>93.16873554199704</v>
       </c>
       <c r="O11" t="n">
-        <v>9.654644777171399</v>
+        <v>9.652395326653226</v>
       </c>
       <c r="P11" t="n">
-        <v>389.3605871936568</v>
+        <v>389.2845635696726</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34273,28 +34401,28 @@
         <v>0.0854</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4962742490895442</v>
+        <v>-0.4892040750859506</v>
       </c>
       <c r="J12" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K12" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1537369807315061</v>
+        <v>0.1503282673275856</v>
       </c>
       <c r="M12" t="n">
-        <v>6.510306861788608</v>
+        <v>6.536730693979337</v>
       </c>
       <c r="N12" t="n">
-        <v>69.38652990543768</v>
+        <v>69.46610004416799</v>
       </c>
       <c r="O12" t="n">
-        <v>8.329857736206405</v>
+        <v>8.334632568036097</v>
       </c>
       <c r="P12" t="n">
-        <v>384.6397628032252</v>
+        <v>384.5596268922546</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34351,28 +34479,28 @@
         <v>0.102</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1192652877621302</v>
+        <v>-0.1111012183440084</v>
       </c>
       <c r="J13" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K13" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01663487827696331</v>
+        <v>0.01441698025022109</v>
       </c>
       <c r="M13" t="n">
-        <v>4.923207428898115</v>
+        <v>4.963076295938166</v>
       </c>
       <c r="N13" t="n">
-        <v>43.34315696061026</v>
+        <v>43.64409921909351</v>
       </c>
       <c r="O13" t="n">
-        <v>6.583552001815605</v>
+        <v>6.606368080806088</v>
       </c>
       <c r="P13" t="n">
-        <v>379.417303689662</v>
+        <v>379.3251864697646</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34429,28 +34557,28 @@
         <v>0.0586</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.029875610549402</v>
+        <v>-0.0222536585732276</v>
       </c>
       <c r="J14" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K14" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0009032602538784351</v>
+        <v>0.0005009377943580029</v>
       </c>
       <c r="M14" t="n">
-        <v>5.262482938759643</v>
+        <v>5.295851596095244</v>
       </c>
       <c r="N14" t="n">
-        <v>50.88918163628453</v>
+        <v>51.1058263955981</v>
       </c>
       <c r="O14" t="n">
-        <v>7.133665371762579</v>
+        <v>7.148833918591066</v>
       </c>
       <c r="P14" t="n">
-        <v>383.337903313371</v>
+        <v>383.2519067188501</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34507,28 +34635,28 @@
         <v>0.0416</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.04830447437007934</v>
+        <v>-0.04530753100281713</v>
       </c>
       <c r="J15" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="K15" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003613652199463413</v>
+        <v>0.003197528224604951</v>
       </c>
       <c r="M15" t="n">
-        <v>4.566137509457621</v>
+        <v>4.563905804708493</v>
       </c>
       <c r="N15" t="n">
-        <v>33.03483153931077</v>
+        <v>32.96983807400252</v>
       </c>
       <c r="O15" t="n">
-        <v>5.747593543328439</v>
+        <v>5.741936787705218</v>
       </c>
       <c r="P15" t="n">
-        <v>392.172378588481</v>
+        <v>392.1384462083651</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34566,7 +34694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P510"/>
+  <dimension ref="A1:P512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76313,6 +76441,170 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-40.727890542400075,172.3146794539428</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-40.72737021206247,172.31525921816143</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-40.727037685091204,172.31611622093422</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-40.726606905917315,172.31682819217167</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-40.72609652766613,172.31740512673824</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-40.7255784132272,172.31796816749488</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-40.72505431758695,172.3185401976774</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-40.72454173849242,172.31913240927543</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>-40.72402927297994,172.31972012825284</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>-40.72350259565957,172.32028478935038</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-40.722974046052855,172.3208510891858</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>-40.72240331965015,172.3213465006343</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>-40.72181355523106,172.32185391064056</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>-40.72130284227101,172.32247640637863</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:19:16+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-40.72788892490354,172.31467706623192</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-40.72737590322628,172.3152676193354</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-40.727053021151214,172.31613885993224</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-40.72662122347459,172.31684932777503</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-40.72611280531395,172.31743029828775</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-40.72559324941746,172.31799229502167</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-40.72506963023753,172.31856518900864</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-40.72455219171934,172.31914946971168</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-40.72404388619092,172.3197443382443</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>-40.72351851366447,172.32031156705494</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-40.72298341791933,172.32086685861137</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>-40.722408033289916,172.32135443195685</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>-40.721828470032705,172.3218764045123</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>-40.72131188265841,172.32248863371376</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0317/nzd0317.xlsx
+++ b/data/nzd0317/nzd0317.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P512"/>
+  <dimension ref="A1:P517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28069,6 +28069,276 @@
         </is>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>428.76</v>
+      </c>
+      <c r="C513" t="n">
+        <v>429.56</v>
+      </c>
+      <c r="D513" t="n">
+        <v>399.54</v>
+      </c>
+      <c r="E513" t="n">
+        <v>386.77</v>
+      </c>
+      <c r="F513" t="n">
+        <v>387.14</v>
+      </c>
+      <c r="G513" t="n">
+        <v>386.61</v>
+      </c>
+      <c r="H513" t="n">
+        <v>385.86</v>
+      </c>
+      <c r="I513" t="n">
+        <v>383.31</v>
+      </c>
+      <c r="J513" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="K513" t="n">
+        <v>377.26</v>
+      </c>
+      <c r="L513" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="M513" t="n">
+        <v>385.62</v>
+      </c>
+      <c r="N513" t="n">
+        <v>388.18</v>
+      </c>
+      <c r="O513" t="n">
+        <v>389.92</v>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>427.34</v>
+      </c>
+      <c r="C514" t="n">
+        <v>427.02</v>
+      </c>
+      <c r="D514" t="n">
+        <v>394.88</v>
+      </c>
+      <c r="E514" t="n">
+        <v>384.12</v>
+      </c>
+      <c r="F514" t="n">
+        <v>383.65</v>
+      </c>
+      <c r="G514" t="n">
+        <v>384.07</v>
+      </c>
+      <c r="H514" t="n">
+        <v>383.68</v>
+      </c>
+      <c r="I514" t="n">
+        <v>380.85</v>
+      </c>
+      <c r="J514" t="n">
+        <v>375.74</v>
+      </c>
+      <c r="K514" t="n">
+        <v>374.54</v>
+      </c>
+      <c r="L514" t="n">
+        <v>377.09</v>
+      </c>
+      <c r="M514" t="n">
+        <v>385.19</v>
+      </c>
+      <c r="N514" t="n">
+        <v>387.2</v>
+      </c>
+      <c r="O514" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>428.04</v>
+      </c>
+      <c r="C515" t="n">
+        <v>427.19</v>
+      </c>
+      <c r="D515" t="n">
+        <v>394.83</v>
+      </c>
+      <c r="E515" t="n">
+        <v>383.64</v>
+      </c>
+      <c r="F515" t="n">
+        <v>383.71</v>
+      </c>
+      <c r="G515" t="n">
+        <v>384.13</v>
+      </c>
+      <c r="H515" t="n">
+        <v>383.37</v>
+      </c>
+      <c r="I515" t="n">
+        <v>380.56</v>
+      </c>
+      <c r="J515" t="n">
+        <v>375.43</v>
+      </c>
+      <c r="K515" t="n">
+        <v>374.54</v>
+      </c>
+      <c r="L515" t="n">
+        <v>377.29</v>
+      </c>
+      <c r="M515" t="n">
+        <v>384.94</v>
+      </c>
+      <c r="N515" t="n">
+        <v>387.75</v>
+      </c>
+      <c r="O515" t="n">
+        <v>391.27</v>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>427.66</v>
+      </c>
+      <c r="C516" t="n">
+        <v>426.49</v>
+      </c>
+      <c r="D516" t="n">
+        <v>392.12</v>
+      </c>
+      <c r="E516" t="n">
+        <v>381.85</v>
+      </c>
+      <c r="F516" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="G516" t="n">
+        <v>384.17</v>
+      </c>
+      <c r="H516" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="I516" t="n">
+        <v>380.74</v>
+      </c>
+      <c r="J516" t="n">
+        <v>374.91</v>
+      </c>
+      <c r="K516" t="n">
+        <v>373.12</v>
+      </c>
+      <c r="L516" t="n">
+        <v>376.07</v>
+      </c>
+      <c r="M516" t="n">
+        <v>383.47</v>
+      </c>
+      <c r="N516" t="n">
+        <v>385.95</v>
+      </c>
+      <c r="O516" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>423.19</v>
+      </c>
+      <c r="C517" t="n">
+        <v>422.36</v>
+      </c>
+      <c r="D517" t="n">
+        <v>391.44</v>
+      </c>
+      <c r="E517" t="n">
+        <v>381.52</v>
+      </c>
+      <c r="F517" t="n">
+        <v>382.26</v>
+      </c>
+      <c r="G517" t="n">
+        <v>381.28</v>
+      </c>
+      <c r="H517" t="n">
+        <v>383.09</v>
+      </c>
+      <c r="I517" t="n">
+        <v>381.09</v>
+      </c>
+      <c r="J517" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="K517" t="n">
+        <v>374.33</v>
+      </c>
+      <c r="L517" t="n">
+        <v>375.94</v>
+      </c>
+      <c r="M517" t="n">
+        <v>383.29</v>
+      </c>
+      <c r="N517" t="n">
+        <v>385.8</v>
+      </c>
+      <c r="O517" t="n">
+        <v>389.36</v>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28080,7 +28350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B537"/>
+  <dimension ref="A1:B542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33453,6 +33723,56 @@
       </c>
       <c r="B537" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -33621,28 +33941,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>1.544999543481225</v>
+        <v>1.513235010017309</v>
       </c>
       <c r="J2" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K2" t="n">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3444715193984792</v>
+        <v>0.3364018224815567</v>
       </c>
       <c r="M2" t="n">
-        <v>11.38691037514766</v>
+        <v>11.44712777616462</v>
       </c>
       <c r="N2" t="n">
-        <v>235.0362853279478</v>
+        <v>235.6719585123831</v>
       </c>
       <c r="O2" t="n">
-        <v>15.33089316797778</v>
+        <v>15.35161094192994</v>
       </c>
       <c r="P2" t="n">
-        <v>403.6022147094378</v>
+        <v>403.9624420435485</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33699,28 +34019,28 @@
         <v>0.0436</v>
       </c>
       <c r="I3" t="n">
-        <v>1.04733389703666</v>
+        <v>1.077573943110287</v>
       </c>
       <c r="J3" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K3" t="n">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1772155328406769</v>
+        <v>0.1868820580921143</v>
       </c>
       <c r="M3" t="n">
-        <v>13.79100798670189</v>
+        <v>13.84953397685399</v>
       </c>
       <c r="N3" t="n">
-        <v>261.8495750410178</v>
+        <v>261.9470188270913</v>
       </c>
       <c r="O3" t="n">
-        <v>16.18176674658913</v>
+        <v>16.18477737959628</v>
       </c>
       <c r="P3" t="n">
-        <v>382.2811897224232</v>
+        <v>381.937144929839</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33777,28 +34097,28 @@
         <v>0.0762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09221146724080481</v>
+        <v>0.104750267335078</v>
       </c>
       <c r="J4" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K4" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004938004238803084</v>
+        <v>0.0064405279103944</v>
       </c>
       <c r="M4" t="n">
-        <v>7.57671796473536</v>
+        <v>7.584599634084731</v>
       </c>
       <c r="N4" t="n">
-        <v>87.99354472088342</v>
+        <v>87.66323086284324</v>
       </c>
       <c r="O4" t="n">
-        <v>9.380487445803839</v>
+        <v>9.362864458211666</v>
       </c>
       <c r="P4" t="n">
-        <v>385.2598934306466</v>
+        <v>385.1172511824494</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33855,28 +34175,28 @@
         <v>0.0934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.345477899233979</v>
+        <v>-0.3402296993420642</v>
       </c>
       <c r="J5" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K5" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09939249011327866</v>
+        <v>0.09810021042345629</v>
       </c>
       <c r="M5" t="n">
-        <v>5.931986485781385</v>
+        <v>5.908551070468545</v>
       </c>
       <c r="N5" t="n">
-        <v>55.50683458252881</v>
+        <v>55.07819269516336</v>
       </c>
       <c r="O5" t="n">
-        <v>7.450290905899501</v>
+        <v>7.421468365166247</v>
       </c>
       <c r="P5" t="n">
-        <v>389.8454398435692</v>
+        <v>389.7856599079365</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33933,28 +34253,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4147348181613578</v>
+        <v>-0.4065267631456601</v>
       </c>
       <c r="J6" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K6" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1133341829112804</v>
+        <v>0.1108424030265369</v>
       </c>
       <c r="M6" t="n">
-        <v>6.258521918079136</v>
+        <v>6.258155881409927</v>
       </c>
       <c r="N6" t="n">
-        <v>69.10704279546765</v>
+        <v>68.65716812133547</v>
       </c>
       <c r="O6" t="n">
-        <v>8.313064585065344</v>
+        <v>8.285962111990102</v>
       </c>
       <c r="P6" t="n">
-        <v>390.2863566467207</v>
+        <v>390.192976838814</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34011,28 +34331,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4029836287503091</v>
+        <v>-0.392398954667223</v>
       </c>
       <c r="J7" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K7" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1124437747107067</v>
+        <v>0.1084807877251045</v>
       </c>
       <c r="M7" t="n">
-        <v>6.127631760343026</v>
+        <v>6.138910119240317</v>
       </c>
       <c r="N7" t="n">
-        <v>65.82904150198966</v>
+        <v>65.53425268180239</v>
       </c>
       <c r="O7" t="n">
-        <v>8.113509814007109</v>
+        <v>8.095322889286281</v>
       </c>
       <c r="P7" t="n">
-        <v>388.9160532373857</v>
+        <v>388.795625668146</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34089,28 +34409,28 @@
         <v>0.0761</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4231502851470579</v>
+        <v>-0.4167608384234665</v>
       </c>
       <c r="J8" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K8" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1191474925318584</v>
+        <v>0.1176730637390033</v>
       </c>
       <c r="M8" t="n">
-        <v>6.408582856899993</v>
+        <v>6.389712079952186</v>
       </c>
       <c r="N8" t="n">
-        <v>67.98135719572741</v>
+        <v>67.44675726572972</v>
       </c>
       <c r="O8" t="n">
-        <v>8.245080787701683</v>
+        <v>8.212597473742989</v>
       </c>
       <c r="P8" t="n">
-        <v>391.5518019913379</v>
+        <v>391.4791028824267</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34167,28 +34487,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5268239617218285</v>
+        <v>-0.5248966715768559</v>
       </c>
       <c r="J9" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K9" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1652115347500653</v>
+        <v>0.1666717750155692</v>
       </c>
       <c r="M9" t="n">
-        <v>6.365977252850501</v>
+        <v>6.316396080495425</v>
       </c>
       <c r="N9" t="n">
-        <v>72.01938040318994</v>
+        <v>71.34055113528464</v>
       </c>
       <c r="O9" t="n">
-        <v>8.48642329860996</v>
+        <v>8.446333591285905</v>
       </c>
       <c r="P9" t="n">
-        <v>394.1858527468613</v>
+        <v>394.1639319303466</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34245,28 +34565,28 @@
         <v>0.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5705277464740909</v>
+        <v>-0.5730991370015591</v>
       </c>
       <c r="J10" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K10" t="n">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1695785557345795</v>
+        <v>0.1733691002294094</v>
       </c>
       <c r="M10" t="n">
-        <v>6.792197087953901</v>
+        <v>6.742524344401229</v>
       </c>
       <c r="N10" t="n">
-        <v>81.88029772774156</v>
+        <v>81.12118310875078</v>
       </c>
       <c r="O10" t="n">
-        <v>9.048773271982316</v>
+        <v>9.006729878749045</v>
       </c>
       <c r="P10" t="n">
-        <v>392.4144846173681</v>
+        <v>392.443786695416</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34323,28 +34643,28 @@
         <v>0.0771</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6055788684054152</v>
+        <v>-0.6028571100674223</v>
       </c>
       <c r="J11" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K11" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1681505279191686</v>
+        <v>0.1693763722959416</v>
       </c>
       <c r="M11" t="n">
-        <v>7.383007785817722</v>
+        <v>7.331318181714927</v>
       </c>
       <c r="N11" t="n">
-        <v>93.16873554199704</v>
+        <v>92.30283065660245</v>
       </c>
       <c r="O11" t="n">
-        <v>9.652395326653226</v>
+        <v>9.607436216629411</v>
       </c>
       <c r="P11" t="n">
-        <v>389.2845635696726</v>
+        <v>389.2536093664666</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34401,28 +34721,28 @@
         <v>0.0854</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4892040750859506</v>
+        <v>-0.479525689437049</v>
       </c>
       <c r="J12" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K12" t="n">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1503282673275856</v>
+        <v>0.1470705654232972</v>
       </c>
       <c r="M12" t="n">
-        <v>6.536730693979337</v>
+        <v>6.543877076936639</v>
       </c>
       <c r="N12" t="n">
-        <v>69.46610004416799</v>
+        <v>69.06307133278426</v>
       </c>
       <c r="O12" t="n">
-        <v>8.334632568036097</v>
+        <v>8.310419443853858</v>
       </c>
       <c r="P12" t="n">
-        <v>384.5596268922546</v>
+        <v>384.4494963738128</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34479,28 +34799,28 @@
         <v>0.102</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1111012183440084</v>
+        <v>-0.09635752347180736</v>
       </c>
       <c r="J13" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K13" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01441698025022109</v>
+        <v>0.01092283587108744</v>
       </c>
       <c r="M13" t="n">
-        <v>4.963076295938166</v>
+        <v>5.022073140499864</v>
       </c>
       <c r="N13" t="n">
-        <v>43.64409921909351</v>
+        <v>43.85034840202488</v>
       </c>
       <c r="O13" t="n">
-        <v>6.606368080806088</v>
+        <v>6.621959559075009</v>
       </c>
       <c r="P13" t="n">
-        <v>379.3251864697646</v>
+        <v>379.1581681350067</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34557,28 +34877,28 @@
         <v>0.0586</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0222536585732276</v>
+        <v>-0.01442151536761401</v>
       </c>
       <c r="J14" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K14" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0005009377943580029</v>
+        <v>0.0002135100095157494</v>
       </c>
       <c r="M14" t="n">
-        <v>5.295851596095244</v>
+        <v>5.299818164439162</v>
       </c>
       <c r="N14" t="n">
-        <v>51.1058263955981</v>
+        <v>50.79463459241419</v>
       </c>
       <c r="O14" t="n">
-        <v>7.148833918591066</v>
+        <v>7.127035470124601</v>
       </c>
       <c r="P14" t="n">
-        <v>383.2519067188501</v>
+        <v>383.1631923653858</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34635,28 +34955,28 @@
         <v>0.0416</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.04530753100281713</v>
+        <v>-0.04730234630202506</v>
       </c>
       <c r="J15" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K15" t="n">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003197528224604951</v>
+        <v>0.003545815867579516</v>
       </c>
       <c r="M15" t="n">
-        <v>4.563905804708493</v>
+        <v>4.531225007137998</v>
       </c>
       <c r="N15" t="n">
-        <v>32.96983807400252</v>
+        <v>32.66705561854962</v>
       </c>
       <c r="O15" t="n">
-        <v>5.741936787705218</v>
+        <v>5.715510092594503</v>
       </c>
       <c r="P15" t="n">
-        <v>392.1384462083651</v>
+        <v>392.1611354649088</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34694,7 +35014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P512"/>
+  <dimension ref="A1:P517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76605,6 +76925,416 @@
         </is>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-40.727925108888336,172.31473048023614</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-40.727409870475626,172.315317761109</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-40.72707926018119,172.316177593867</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-40.72664530571706,172.3168848780572</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-40.72613824277419,172.31746963449723</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-40.72561680610625,172.31803060439927</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-40.72508935021134,172.31859737343365</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-40.72457162906436,172.31918119291552</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-40.72406723372446,172.31978301859752</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-40.72353809224741,172.32034450271604</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-40.72299450888281,172.32088552065923</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>-40.72241496511212,172.3213660956685</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>-40.72184859317086,172.32190675340277</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>-40.72133875269117,172.3225249760906</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-40.72793361571565,172.31474303784157</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-40.727425086837805,172.31534022322512</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-40.72710717657796,172.3162188039772</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-40.72666118082122,172.31690831295876</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-40.72615860440139,172.31750112153057</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-40.72563118927061,172.31805399523446</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-40.725101668127444,172.31861747718156</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-40.72458552902089,172.31920387870633</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-40.724083526599976,172.31981001137805</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>-40.72355317828797,172.3203698809157</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-40.72300066436625,172.32089587809847</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>-40.722417349658684,172.32137010798587</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>-40.72185439336806,172.32191550102755</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>-40.72133799932591,172.32252395714505</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:13:04+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-40.727929422209385,172.3147368474723</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-40.72742406842,172.31533871985485</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-40.72710747611002,172.31621924614595</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-40.726664056311286,172.3169125577723</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-40.72615825434484,172.31750058020606</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-40.72563084951087,172.31805344269495</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-40.72510341975744,172.318620335972</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-40.724587167633366,172.31920655304816</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-40.724085262266755,172.3198128868984</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>-40.72355317828797,172.3203698809157</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>-40.722999555270206,172.32089401189305</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>-40.72241873602291,172.32137244072868</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>-40.72185113815544,172.32191059164612</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>-40.72133027733159,172.32251351295457</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-40.72793169868425,172.31474020795835</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-40.727428261904954,172.31534491020344</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-40.72712371074598,172.31624321169824</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-40.72667477949162,172.31692838739272</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-40.726166480673236,172.31751330133372</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-40.72563062300439,172.31805307433527</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-40.725103815286786,172.31862098150538</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-40.72458615056357,172.31920489311184</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-40.724088173707656,172.31981771035225</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>-40.723561054086375,172.32038312983332</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>-40.72300632075564,172.32090539574702</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>-40.72242688784358,172.32138615725825</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>-40.721861791577815,172.32192665871443</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>-40.72134672580618,172.32253575993235</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:19:21+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-40.727958477210244,172.31477973790393</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-40.72745300345956,172.31538143327595</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-40.7271277843808,172.31624922519654</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-40.72667675639054,172.31693130570318</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-40.72616671404423,172.31751366221684</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-40.72564698809534,172.31807968832888</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-40.72510500187479,172.31862291810543</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-40.72458417292778,172.31920166545802</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-40.72408828568615,172.3198178958697</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>-40.72355434301881,172.32037184026248</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>-40.72300704166794,172.32090660878077</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>-40.72242788602557,172.32138783683354</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>-40.72186267936291,172.321927997637</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>-40.72134226839554,172.3225297311701</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0317/nzd0317.xlsx
+++ b/data/nzd0317/nzd0317.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P517"/>
+  <dimension ref="A1:P520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28339,6 +28339,168 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>422.98</v>
+      </c>
+      <c r="C518" t="n">
+        <v>417.52</v>
+      </c>
+      <c r="D518" t="n">
+        <v>388.94</v>
+      </c>
+      <c r="E518" t="n">
+        <v>378.52</v>
+      </c>
+      <c r="F518" t="n">
+        <v>378.82</v>
+      </c>
+      <c r="G518" t="n">
+        <v>377.13</v>
+      </c>
+      <c r="H518" t="n">
+        <v>378.84</v>
+      </c>
+      <c r="I518" t="n">
+        <v>377.23</v>
+      </c>
+      <c r="J518" t="n">
+        <v>371.3</v>
+      </c>
+      <c r="K518" t="n">
+        <v>370.45</v>
+      </c>
+      <c r="L518" t="n">
+        <v>375.35</v>
+      </c>
+      <c r="M518" t="n">
+        <v>385.53</v>
+      </c>
+      <c r="N518" t="n">
+        <v>384.41</v>
+      </c>
+      <c r="O518" t="n">
+        <v>389.41</v>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>423.61</v>
+      </c>
+      <c r="C519" t="n">
+        <v>417.32</v>
+      </c>
+      <c r="D519" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="E519" t="n">
+        <v>378.01</v>
+      </c>
+      <c r="F519" t="n">
+        <v>377.97</v>
+      </c>
+      <c r="G519" t="n">
+        <v>376.58</v>
+      </c>
+      <c r="H519" t="n">
+        <v>378.81</v>
+      </c>
+      <c r="I519" t="n">
+        <v>377.18</v>
+      </c>
+      <c r="J519" t="n">
+        <v>371.12</v>
+      </c>
+      <c r="K519" t="n">
+        <v>370.6</v>
+      </c>
+      <c r="L519" t="n">
+        <v>375.66</v>
+      </c>
+      <c r="M519" t="n">
+        <v>385.37</v>
+      </c>
+      <c r="N519" t="n">
+        <v>385.45</v>
+      </c>
+      <c r="O519" t="n">
+        <v>390.64</v>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>425.74</v>
+      </c>
+      <c r="C520" t="n">
+        <v>418.46</v>
+      </c>
+      <c r="D520" t="n">
+        <v>388.67</v>
+      </c>
+      <c r="E520" t="n">
+        <v>377.94</v>
+      </c>
+      <c r="F520" t="n">
+        <v>377.36</v>
+      </c>
+      <c r="G520" t="n">
+        <v>376.08</v>
+      </c>
+      <c r="H520" t="n">
+        <v>378.34</v>
+      </c>
+      <c r="I520" t="n">
+        <v>377.44</v>
+      </c>
+      <c r="J520" t="n">
+        <v>371.23</v>
+      </c>
+      <c r="K520" t="n">
+        <v>370.09</v>
+      </c>
+      <c r="L520" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="M520" t="n">
+        <v>385.87</v>
+      </c>
+      <c r="N520" t="n">
+        <v>385.91</v>
+      </c>
+      <c r="O520" t="n">
+        <v>391.32</v>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28350,7 +28512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B542"/>
+  <dimension ref="A1:B545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33773,6 +33935,36 @@
       </c>
       <c r="B542" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -33941,28 +34133,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>1.513235010017309</v>
+        <v>1.491605514372112</v>
       </c>
       <c r="J2" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K2" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3364018224815567</v>
+        <v>0.3302231037964075</v>
       </c>
       <c r="M2" t="n">
-        <v>11.44712777616462</v>
+        <v>11.49837051074243</v>
       </c>
       <c r="N2" t="n">
-        <v>235.6719585123831</v>
+        <v>236.5919719524208</v>
       </c>
       <c r="O2" t="n">
-        <v>15.35161094192994</v>
+        <v>15.3815464746696</v>
       </c>
       <c r="P2" t="n">
-        <v>403.9624420435485</v>
+        <v>404.2086364327531</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34019,28 +34211,28 @@
         <v>0.0436</v>
       </c>
       <c r="I3" t="n">
-        <v>1.077573943110287</v>
+        <v>1.085459255839562</v>
       </c>
       <c r="J3" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K3" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1868820580921143</v>
+        <v>0.1905821898431788</v>
       </c>
       <c r="M3" t="n">
-        <v>13.84953397685399</v>
+        <v>13.81943348923879</v>
       </c>
       <c r="N3" t="n">
-        <v>261.9470188270913</v>
+        <v>260.7283094611367</v>
       </c>
       <c r="O3" t="n">
-        <v>16.18477737959628</v>
+        <v>16.14708362092476</v>
       </c>
       <c r="P3" t="n">
-        <v>381.937144929839</v>
+        <v>381.8470734505721</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34097,28 +34289,28 @@
         <v>0.0762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.104750267335078</v>
+        <v>0.1055921096613515</v>
       </c>
       <c r="J4" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K4" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0064405279103944</v>
+        <v>0.006613777156405765</v>
       </c>
       <c r="M4" t="n">
-        <v>7.584599634084731</v>
+        <v>7.546067988787621</v>
       </c>
       <c r="N4" t="n">
-        <v>87.66323086284324</v>
+        <v>87.15922094675655</v>
       </c>
       <c r="O4" t="n">
-        <v>9.362864458211666</v>
+        <v>9.335910290205051</v>
       </c>
       <c r="P4" t="n">
-        <v>385.1172511824494</v>
+        <v>385.1076352317189</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34175,28 +34367,28 @@
         <v>0.0934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3402296993420642</v>
+        <v>-0.3430686501498065</v>
       </c>
       <c r="J5" t="n">
+        <v>519</v>
+      </c>
+      <c r="K5" t="n">
         <v>516</v>
       </c>
-      <c r="K5" t="n">
-        <v>513</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.09810021042345629</v>
+        <v>0.100482428032806</v>
       </c>
       <c r="M5" t="n">
-        <v>5.908551070468545</v>
+        <v>5.885635774630479</v>
       </c>
       <c r="N5" t="n">
-        <v>55.07819269516336</v>
+        <v>54.79716832960601</v>
       </c>
       <c r="O5" t="n">
-        <v>7.421468365166247</v>
+        <v>7.402510947618112</v>
       </c>
       <c r="P5" t="n">
-        <v>389.7856599079365</v>
+        <v>389.8181447073447</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34253,28 +34445,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4065267631456601</v>
+        <v>-0.4080093142139787</v>
       </c>
       <c r="J6" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K6" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1108424030265369</v>
+        <v>0.1126137095767684</v>
       </c>
       <c r="M6" t="n">
-        <v>6.258155881409927</v>
+        <v>6.226630475969219</v>
       </c>
       <c r="N6" t="n">
-        <v>68.65716812133547</v>
+        <v>68.27212746112187</v>
       </c>
       <c r="O6" t="n">
-        <v>8.285962111990102</v>
+        <v>8.262694927269303</v>
       </c>
       <c r="P6" t="n">
-        <v>390.192976838814</v>
+        <v>390.2099202872779</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34331,28 +34523,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.392398954667223</v>
+        <v>-0.3943508064254385</v>
       </c>
       <c r="J7" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K7" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1084807877251045</v>
+        <v>0.1104674536712594</v>
       </c>
       <c r="M7" t="n">
-        <v>6.138910119240317</v>
+        <v>6.110877331323143</v>
       </c>
       <c r="N7" t="n">
-        <v>65.53425268180239</v>
+        <v>65.17406314897292</v>
       </c>
       <c r="O7" t="n">
-        <v>8.095322889286281</v>
+        <v>8.073045469274462</v>
       </c>
       <c r="P7" t="n">
-        <v>388.795625668146</v>
+        <v>388.8179285474712</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34409,28 +34601,28 @@
         <v>0.0761</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4167608384234665</v>
+        <v>-0.4186769719447434</v>
       </c>
       <c r="J8" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K8" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1176730637390033</v>
+        <v>0.1197295408575066</v>
       </c>
       <c r="M8" t="n">
-        <v>6.389712079952186</v>
+        <v>6.359912962062182</v>
       </c>
       <c r="N8" t="n">
-        <v>67.44675726572972</v>
+        <v>67.0740902426903</v>
       </c>
       <c r="O8" t="n">
-        <v>8.212597473742989</v>
+        <v>8.18987730327447</v>
       </c>
       <c r="P8" t="n">
-        <v>391.4791028824267</v>
+        <v>391.5009951263561</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34487,28 +34679,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5248966715768559</v>
+        <v>-0.528119522111651</v>
       </c>
       <c r="J9" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K9" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1666717750155692</v>
+        <v>0.1697905051486625</v>
       </c>
       <c r="M9" t="n">
-        <v>6.316396080495425</v>
+        <v>6.293455276184232</v>
       </c>
       <c r="N9" t="n">
-        <v>71.34055113528464</v>
+        <v>70.97747902331994</v>
       </c>
       <c r="O9" t="n">
-        <v>8.446333591285905</v>
+        <v>8.424813293083707</v>
       </c>
       <c r="P9" t="n">
-        <v>394.1639319303466</v>
+        <v>394.2007490236653</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34565,28 +34757,28 @@
         <v>0.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5730991370015591</v>
+        <v>-0.579656973199644</v>
       </c>
       <c r="J10" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K10" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1733691002294094</v>
+        <v>0.1778466236738317</v>
       </c>
       <c r="M10" t="n">
-        <v>6.742524344401229</v>
+        <v>6.732074874217805</v>
       </c>
       <c r="N10" t="n">
-        <v>81.12118310875078</v>
+        <v>80.85778010426803</v>
       </c>
       <c r="O10" t="n">
-        <v>9.006729878749045</v>
+        <v>8.99209542344097</v>
       </c>
       <c r="P10" t="n">
-        <v>392.443786695416</v>
+        <v>392.518736201283</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34643,28 +34835,28 @@
         <v>0.0771</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6028571100674223</v>
+        <v>-0.6059892901192796</v>
       </c>
       <c r="J11" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K11" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1693763722959416</v>
+        <v>0.1722941920516258</v>
       </c>
       <c r="M11" t="n">
-        <v>7.331318181714927</v>
+        <v>7.299601596072725</v>
       </c>
       <c r="N11" t="n">
-        <v>92.30283065660245</v>
+        <v>91.81573043158686</v>
       </c>
       <c r="O11" t="n">
-        <v>9.607436216629411</v>
+        <v>9.582052516636864</v>
       </c>
       <c r="P11" t="n">
-        <v>389.2536093664666</v>
+        <v>389.2893931433633</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34721,28 +34913,28 @@
         <v>0.0854</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.479525689437049</v>
+        <v>-0.4753221858314629</v>
       </c>
       <c r="J12" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K12" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1470705654232972</v>
+        <v>0.14605764071968</v>
       </c>
       <c r="M12" t="n">
-        <v>6.543877076936639</v>
+        <v>6.536642862704524</v>
       </c>
       <c r="N12" t="n">
-        <v>69.06307133278426</v>
+        <v>68.74834983840992</v>
       </c>
       <c r="O12" t="n">
-        <v>8.310419443853858</v>
+        <v>8.291462466803424</v>
       </c>
       <c r="P12" t="n">
-        <v>384.4494963738128</v>
+        <v>384.4014730998367</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34799,28 +34991,28 @@
         <v>0.102</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09635752347180736</v>
+        <v>-0.08663847585110049</v>
       </c>
       <c r="J13" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K13" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01092283587108744</v>
+        <v>0.008851092326467858</v>
       </c>
       <c r="M13" t="n">
-        <v>5.022073140499864</v>
+        <v>5.063486649561342</v>
       </c>
       <c r="N13" t="n">
-        <v>43.85034840202488</v>
+        <v>44.05642197273713</v>
       </c>
       <c r="O13" t="n">
-        <v>6.621959559075009</v>
+        <v>6.637501184386871</v>
       </c>
       <c r="P13" t="n">
-        <v>379.1581681350067</v>
+        <v>379.0476341569146</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34877,28 +35069,28 @@
         <v>0.0586</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01442151536761401</v>
+        <v>-0.01174165284839356</v>
       </c>
       <c r="J14" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="K14" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0002135100095157494</v>
+        <v>0.0001429625482608499</v>
       </c>
       <c r="M14" t="n">
-        <v>5.299818164439162</v>
+        <v>5.288130150946203</v>
       </c>
       <c r="N14" t="n">
-        <v>50.79463459241419</v>
+        <v>50.53818946540291</v>
       </c>
       <c r="O14" t="n">
-        <v>7.127035470124601</v>
+        <v>7.109021695381363</v>
       </c>
       <c r="P14" t="n">
-        <v>383.1631923653858</v>
+        <v>383.132708000812</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34955,28 +35147,28 @@
         <v>0.0416</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.04730234630202506</v>
+        <v>-0.04779036816968178</v>
       </c>
       <c r="J15" t="n">
+        <v>519</v>
+      </c>
+      <c r="K15" t="n">
         <v>516</v>
       </c>
-      <c r="K15" t="n">
-        <v>513</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.003545815867579516</v>
+        <v>0.003657467002404546</v>
       </c>
       <c r="M15" t="n">
-        <v>4.531225007137998</v>
+        <v>4.509062463683446</v>
       </c>
       <c r="N15" t="n">
-        <v>32.66705561854962</v>
+        <v>32.48190541385274</v>
       </c>
       <c r="O15" t="n">
-        <v>5.715510092594503</v>
+        <v>5.69928990435236</v>
       </c>
       <c r="P15" t="n">
-        <v>392.1611354649088</v>
+        <v>392.1666964587214</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35014,7 +35206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P517"/>
+  <dimension ref="A1:P520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77335,6 +77527,252 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-40.72795973526147,172.31478159501626</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-40.72748199839031,172.31542423516782</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-40.727142760976726,172.31627133365262</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-40.72669472819567,172.31695783580622</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-40.726186783945906,172.3175446981729</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-40.725670488128834,172.31811790567818</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-40.72512901614896,172.3186621112173</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-40.72460598342047,172.31923726187918</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>-40.72410838582067,172.3198511962645</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>-40.7235758628018,172.32040804153905</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>-40.72301031350061,172.32091211408815</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>-40.722415464203266,172.32136693545584</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>-40.72187090617074,172.32194040498806</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>-40.72134195449337,172.3225293066094</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-40.727955961107696,172.31477602367954</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-40.72748319652762,172.31542600384182</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-40.72714599592089,172.31627610908046</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-40.72669778340193,172.31696234592516</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-40.7261917430773,172.317552366944</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-40.725673602590156,172.31812297063013</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-40.725129185661444,172.31866238787464</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-40.724606265939734,172.31923772297284</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-40.72410939362662,172.31985286592268</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>-40.723575030851634,172.32040664200474</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>-40.72300859440212,172.32090922146895</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>-40.722416351476426,172.32136842841112</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>-40.72186475086141,172.32193112178985</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>-40.72133423249953,172.3225188624177</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-40.72794320087155,172.31475718725997</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-40.72747636714467,172.31541592240077</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-40.727144378448834,172.3162737213665</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-40.72669820274395,172.31696296496114</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-40.72619530198306,172.3175578704157</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-40.72567643391845,172.31812757513228</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-40.72513184135681,172.31866672217348</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>-40.72460479683954,172.31923532528572</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>-40.72410877774521,172.319851845576</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>-40.72357785948212,172.32041140042156</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>-40.72300798439943,172.32090819505572</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>-40.72241357874777,172.32136376292598</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>-40.72186202832051,172.32192701576045</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>-40.72132996342936,172.32251308839403</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0317/nzd0317.xlsx
+++ b/data/nzd0317/nzd0317.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P520"/>
+  <dimension ref="A1:P524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28501,6 +28501,222 @@
         </is>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>428.1</v>
+      </c>
+      <c r="C521" t="n">
+        <v>418.74</v>
+      </c>
+      <c r="D521" t="n">
+        <v>388.21</v>
+      </c>
+      <c r="E521" t="n">
+        <v>377.58</v>
+      </c>
+      <c r="F521" t="n">
+        <v>376.62</v>
+      </c>
+      <c r="G521" t="n">
+        <v>375.59</v>
+      </c>
+      <c r="H521" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="I521" t="n">
+        <v>376.94</v>
+      </c>
+      <c r="J521" t="n">
+        <v>370.64</v>
+      </c>
+      <c r="K521" t="n">
+        <v>369.79</v>
+      </c>
+      <c r="L521" t="n">
+        <v>376.77</v>
+      </c>
+      <c r="M521" t="n">
+        <v>386.95</v>
+      </c>
+      <c r="N521" t="n">
+        <v>386.89</v>
+      </c>
+      <c r="O521" t="n">
+        <v>392.64</v>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>428.87</v>
+      </c>
+      <c r="C522" t="n">
+        <v>418.31</v>
+      </c>
+      <c r="D522" t="n">
+        <v>387.53</v>
+      </c>
+      <c r="E522" t="n">
+        <v>376.28</v>
+      </c>
+      <c r="F522" t="n">
+        <v>374.79</v>
+      </c>
+      <c r="G522" t="n">
+        <v>373.59</v>
+      </c>
+      <c r="H522" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="I522" t="n">
+        <v>375.19</v>
+      </c>
+      <c r="J522" t="n">
+        <v>369.16</v>
+      </c>
+      <c r="K522" t="n">
+        <v>368.94</v>
+      </c>
+      <c r="L522" t="n">
+        <v>376.94</v>
+      </c>
+      <c r="M522" t="n">
+        <v>386.83</v>
+      </c>
+      <c r="N522" t="n">
+        <v>386.86</v>
+      </c>
+      <c r="O522" t="n">
+        <v>393.69</v>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>427.31</v>
+      </c>
+      <c r="C523" t="n">
+        <v>417.76</v>
+      </c>
+      <c r="D523" t="n">
+        <v>387.31</v>
+      </c>
+      <c r="E523" t="n">
+        <v>375.82</v>
+      </c>
+      <c r="F523" t="n">
+        <v>374.16</v>
+      </c>
+      <c r="G523" t="n">
+        <v>372.38</v>
+      </c>
+      <c r="H523" t="n">
+        <v>374.32</v>
+      </c>
+      <c r="I523" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="J523" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="K523" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="L523" t="n">
+        <v>376.08</v>
+      </c>
+      <c r="M523" t="n">
+        <v>385.88</v>
+      </c>
+      <c r="N523" t="n">
+        <v>386.33</v>
+      </c>
+      <c r="O523" t="n">
+        <v>393.44</v>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>427.31</v>
+      </c>
+      <c r="C524" t="n">
+        <v>417.76</v>
+      </c>
+      <c r="D524" t="n">
+        <v>388.09</v>
+      </c>
+      <c r="E524" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="F524" t="n">
+        <v>375.02</v>
+      </c>
+      <c r="G524" t="n">
+        <v>372.77</v>
+      </c>
+      <c r="H524" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="I524" t="n">
+        <v>374.32</v>
+      </c>
+      <c r="J524" t="n">
+        <v>369.13</v>
+      </c>
+      <c r="K524" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="L524" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="M524" t="n">
+        <v>385.35</v>
+      </c>
+      <c r="N524" t="n">
+        <v>386.14</v>
+      </c>
+      <c r="O524" t="n">
+        <v>393.35</v>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28512,7 +28728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B545"/>
+  <dimension ref="A1:B549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33965,6 +34181,46 @@
       </c>
       <c r="B545" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -34133,28 +34389,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>1.491605514372112</v>
+        <v>1.468805993759896</v>
       </c>
       <c r="J2" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K2" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3302231037964075</v>
+        <v>0.3247558391545859</v>
       </c>
       <c r="M2" t="n">
-        <v>11.49837051074243</v>
+        <v>11.53362851584307</v>
       </c>
       <c r="N2" t="n">
-        <v>236.5919719524208</v>
+        <v>236.7026020884093</v>
       </c>
       <c r="O2" t="n">
-        <v>15.3815464746696</v>
+        <v>15.38514225115937</v>
       </c>
       <c r="P2" t="n">
-        <v>404.2086364327531</v>
+        <v>404.469263954954</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34211,28 +34467,28 @@
         <v>0.0436</v>
       </c>
       <c r="I3" t="n">
-        <v>1.085459255839562</v>
+        <v>1.096065877037815</v>
       </c>
       <c r="J3" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K3" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1905821898431788</v>
+        <v>0.1955761230210683</v>
       </c>
       <c r="M3" t="n">
-        <v>13.81943348923879</v>
+        <v>13.78029855756291</v>
       </c>
       <c r="N3" t="n">
-        <v>260.7283094611367</v>
+        <v>259.1406379674283</v>
       </c>
       <c r="O3" t="n">
-        <v>16.14708362092476</v>
+        <v>16.0978457554863</v>
       </c>
       <c r="P3" t="n">
-        <v>381.8470734505721</v>
+        <v>381.725429735733</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34289,28 +34545,28 @@
         <v>0.0762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1055921096613515</v>
+        <v>0.1053994043676049</v>
       </c>
       <c r="J4" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K4" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006613777156405765</v>
+        <v>0.006683475088567259</v>
       </c>
       <c r="M4" t="n">
-        <v>7.546067988787621</v>
+        <v>7.490817008110533</v>
       </c>
       <c r="N4" t="n">
-        <v>87.15922094675655</v>
+        <v>86.49254050494069</v>
       </c>
       <c r="O4" t="n">
-        <v>9.335910290205051</v>
+        <v>9.300136585284148</v>
       </c>
       <c r="P4" t="n">
-        <v>385.1076352317189</v>
+        <v>385.1098480609645</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34367,28 +34623,28 @@
         <v>0.0934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3430686501498065</v>
+        <v>-0.3489328501698655</v>
       </c>
       <c r="J5" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K5" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="L5" t="n">
-        <v>0.100482428032806</v>
+        <v>0.1046916049466662</v>
       </c>
       <c r="M5" t="n">
-        <v>5.885635774630479</v>
+        <v>5.863847695481002</v>
       </c>
       <c r="N5" t="n">
-        <v>54.79716832960601</v>
+        <v>54.50463042968068</v>
       </c>
       <c r="O5" t="n">
-        <v>7.402510947618112</v>
+        <v>7.382725135726013</v>
       </c>
       <c r="P5" t="n">
-        <v>389.8181447073447</v>
+        <v>389.8855294288611</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34445,28 +34701,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4080093142139787</v>
+        <v>-0.4140313310529868</v>
       </c>
       <c r="J6" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K6" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1126137095767684</v>
+        <v>0.116825806217433</v>
       </c>
       <c r="M6" t="n">
-        <v>6.226630475969219</v>
+        <v>6.197874759012754</v>
       </c>
       <c r="N6" t="n">
-        <v>68.27212746112187</v>
+        <v>67.88768681695703</v>
       </c>
       <c r="O6" t="n">
-        <v>8.262694927269303</v>
+        <v>8.239398449945059</v>
       </c>
       <c r="P6" t="n">
-        <v>390.2099202872779</v>
+        <v>390.2790179421123</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34523,28 +34779,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3943508064254385</v>
+        <v>-0.4011456657121487</v>
       </c>
       <c r="J7" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K7" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1104674536712594</v>
+        <v>0.1150291719113913</v>
       </c>
       <c r="M7" t="n">
-        <v>6.110877331323143</v>
+        <v>6.089894602748335</v>
       </c>
       <c r="N7" t="n">
-        <v>65.17406314897292</v>
+        <v>64.85480881577017</v>
       </c>
       <c r="O7" t="n">
-        <v>8.073045469274462</v>
+        <v>8.053248339382698</v>
       </c>
       <c r="P7" t="n">
-        <v>388.8179285474712</v>
+        <v>388.8959044519893</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34601,28 +34857,28 @@
         <v>0.0761</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4186769719447434</v>
+        <v>-0.4253012392132585</v>
       </c>
       <c r="J8" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K8" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1197295408575066</v>
+        <v>0.124325980453005</v>
       </c>
       <c r="M8" t="n">
-        <v>6.359912962062182</v>
+        <v>6.335783641877049</v>
       </c>
       <c r="N8" t="n">
-        <v>67.0740902426903</v>
+        <v>66.74071911707598</v>
       </c>
       <c r="O8" t="n">
-        <v>8.18987730327447</v>
+        <v>8.169499318628773</v>
       </c>
       <c r="P8" t="n">
-        <v>391.5009951263561</v>
+        <v>391.5770248946562</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34679,28 +34935,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.528119522111651</v>
+        <v>-0.5352432990898103</v>
       </c>
       <c r="J9" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K9" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1697905051486625</v>
+        <v>0.1752528563671242</v>
       </c>
       <c r="M9" t="n">
-        <v>6.293455276184232</v>
+        <v>6.27502596779827</v>
       </c>
       <c r="N9" t="n">
-        <v>70.97747902331994</v>
+        <v>70.62772322269869</v>
       </c>
       <c r="O9" t="n">
-        <v>8.424813293083707</v>
+        <v>8.404030177402904</v>
       </c>
       <c r="P9" t="n">
-        <v>394.2007490236653</v>
+        <v>394.2824950850535</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34757,28 +35013,28 @@
         <v>0.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.579656973199644</v>
+        <v>-0.5907214214324459</v>
       </c>
       <c r="J10" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K10" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1778466236738317</v>
+        <v>0.1847326728217941</v>
       </c>
       <c r="M10" t="n">
-        <v>6.732074874217805</v>
+        <v>6.728320405841939</v>
       </c>
       <c r="N10" t="n">
-        <v>80.85778010426803</v>
+        <v>80.68950880496784</v>
       </c>
       <c r="O10" t="n">
-        <v>8.99209542344097</v>
+        <v>8.982733927094126</v>
       </c>
       <c r="P10" t="n">
-        <v>392.518736201283</v>
+        <v>392.6457325916234</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34835,28 +35091,28 @@
         <v>0.0771</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6059892901192796</v>
+        <v>-0.6119603434402564</v>
       </c>
       <c r="J11" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K11" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1722941920516258</v>
+        <v>0.1769614689386267</v>
       </c>
       <c r="M11" t="n">
-        <v>7.299601596072725</v>
+        <v>7.264181675807451</v>
       </c>
       <c r="N11" t="n">
-        <v>91.81573043158686</v>
+        <v>91.24414914427389</v>
       </c>
       <c r="O11" t="n">
-        <v>9.582052516636864</v>
+        <v>9.552180334576702</v>
       </c>
       <c r="P11" t="n">
-        <v>389.2893931433633</v>
+        <v>389.3579005465226</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34913,28 +35169,28 @@
         <v>0.0854</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4753221858314629</v>
+        <v>-0.4686882590321776</v>
       </c>
       <c r="J12" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K12" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L12" t="n">
-        <v>0.14605764071968</v>
+        <v>0.1440397801015334</v>
       </c>
       <c r="M12" t="n">
-        <v>6.536642862704524</v>
+        <v>6.534441907495265</v>
       </c>
       <c r="N12" t="n">
-        <v>68.74834983840992</v>
+        <v>68.38428241868318</v>
       </c>
       <c r="O12" t="n">
-        <v>8.291462466803424</v>
+        <v>8.269478968996969</v>
       </c>
       <c r="P12" t="n">
-        <v>384.4014730998367</v>
+        <v>384.3253834115379</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34991,28 +35247,28 @@
         <v>0.102</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.08663847585110049</v>
+        <v>-0.07310263062386121</v>
       </c>
       <c r="J13" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K13" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L13" t="n">
-        <v>0.008851092326467858</v>
+        <v>0.00630962960899728</v>
       </c>
       <c r="M13" t="n">
-        <v>5.063486649561342</v>
+        <v>5.122734376752351</v>
       </c>
       <c r="N13" t="n">
-        <v>44.05642197273713</v>
+        <v>44.39998047340697</v>
       </c>
       <c r="O13" t="n">
-        <v>6.637501184386871</v>
+        <v>6.663331034355638</v>
       </c>
       <c r="P13" t="n">
-        <v>379.0476341569146</v>
+        <v>378.8930687863089</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35069,28 +35325,28 @@
         <v>0.0586</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.01174165284839356</v>
+        <v>-0.006429956610919615</v>
       </c>
       <c r="J14" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K14" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001429625482608499</v>
+        <v>4.339824983379259e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>5.288130150946203</v>
+        <v>5.285101698689962</v>
       </c>
       <c r="N14" t="n">
-        <v>50.53818946540291</v>
+        <v>50.25677008450495</v>
       </c>
       <c r="O14" t="n">
-        <v>7.109021695381363</v>
+        <v>7.08920094823845</v>
       </c>
       <c r="P14" t="n">
-        <v>383.132708000812</v>
+        <v>383.0720556392565</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35147,28 +35403,28 @@
         <v>0.0416</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.04779036816968178</v>
+        <v>-0.04437331575019148</v>
       </c>
       <c r="J15" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="K15" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003657467002404546</v>
+        <v>0.003195334441806308</v>
       </c>
       <c r="M15" t="n">
-        <v>4.509062463683446</v>
+        <v>4.492664607289538</v>
       </c>
       <c r="N15" t="n">
-        <v>32.48190541385274</v>
+        <v>32.2761236971192</v>
       </c>
       <c r="O15" t="n">
-        <v>5.69928990435236</v>
+        <v>5.681207943485187</v>
       </c>
       <c r="P15" t="n">
-        <v>392.1666964587214</v>
+        <v>392.1275292151616</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35206,7 +35462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P520"/>
+  <dimension ref="A1:P524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77773,6 +78029,334 @@
         </is>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:12:46+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-40.72792906276599,172.31473631686924</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-40.72747468975223,172.31541344625768</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-40.72714713414195,172.3162777893237</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-40.72670035936002,172.31696614857478</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-40.7261996193438,172.31756454675926</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-40.72567920862,172.3181320875448</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-40.725131502331884,172.31866616885873</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-40.72460762203219,172.31923993622263</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>-40.72411208110899,172.31985731834484</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>-40.72357952338233,172.32041419949047</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>-40.72300243891987,172.32089886402724</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>-40.72240758965325,172.32135368547938</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>-40.721856228124174,172.32191826813366</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>-40.72132167640997,172.32250187999728</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:12:55+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-40.7279244499087,172.31472950746402</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-40.72747726574773,172.31541724890604</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-40.72715120777498,172.31628380282626</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-40.72670814713953,172.31697764495917</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-40.72621029605856,172.3175810571801</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-40.72569053393062,172.31815050555892</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>-40.72514619340992,172.31869014583697</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>-40.724617510204965,172.3192560745049</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>-40.72412036751194,172.31987104664864</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>-40.72358423776584,172.3204221301865</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>-40.72300149618827,172.32089727775255</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>-40.72240825510824,172.3213548051956</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>-40.721856405681216,172.32191853591814</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>-40.72131508446196,172.32249296422913</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-40.727933795437345,172.3147433031431</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-40.72748056062553,172.31542211275908</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-40.727152525715006,172.31628574837134</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-40.72671090281511,172.3169817129112</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-40.726213971648356,172.31758674109668</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>-40.72569738574213,172.3181616484605</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>-40.72515455602139,172.31870379427545</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-40.72462282156542,172.31926474306994</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>-40.724123838842424,172.31987679769588</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>-40.72358645629909,172.32042586227914</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>-40.72300626530084,172.32090530243673</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>-40.72241352329319,172.3213636696163</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>-40.721859542522154,172.32192326677733</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>-40.72131665397346,172.32249508703092</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-40.727933795437345,172.3147433031431</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-40.72748056062553,172.31542211275908</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-40.72714785301839,172.31627885052998</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-40.72670557118182,172.31697384230864</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-40.72620895417651,172.31757898209958</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-40.725695177307124,172.31815805694652</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-40.725153934476,172.31870277986437</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-40.72462242603861,172.31926409753845</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>-40.72412053547956,172.31987132492512</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>-40.7235855688858,172.32042436944207</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>-40.72300798439943,172.32090819505572</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>-40.72241646238556,172.32136861503054</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>-40.721860667049995,172.32192496274587</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>-40.72131721899758,172.32249585123958</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0317/nzd0317.xlsx
+++ b/data/nzd0317/nzd0317.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P524"/>
+  <dimension ref="A1:P528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28717,6 +28717,222 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>427.31</v>
+      </c>
+      <c r="C525" t="n">
+        <v>417.76</v>
+      </c>
+      <c r="D525" t="n">
+        <v>389.2</v>
+      </c>
+      <c r="E525" t="n">
+        <v>378.19</v>
+      </c>
+      <c r="F525" t="n">
+        <v>376.25</v>
+      </c>
+      <c r="G525" t="n">
+        <v>374.05</v>
+      </c>
+      <c r="H525" t="n">
+        <v>374.52</v>
+      </c>
+      <c r="I525" t="n">
+        <v>374.36</v>
+      </c>
+      <c r="J525" t="n">
+        <v>369.69</v>
+      </c>
+      <c r="K525" t="n">
+        <v>369.17</v>
+      </c>
+      <c r="L525" t="n">
+        <v>375.49</v>
+      </c>
+      <c r="M525" t="n">
+        <v>385.17</v>
+      </c>
+      <c r="N525" t="n">
+        <v>386.68</v>
+      </c>
+      <c r="O525" t="n">
+        <v>395.44</v>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:18:41+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>425.44</v>
+      </c>
+      <c r="C526" t="n">
+        <v>417.76</v>
+      </c>
+      <c r="D526" t="n">
+        <v>388.16</v>
+      </c>
+      <c r="E526" t="n">
+        <v>377.21</v>
+      </c>
+      <c r="F526" t="n">
+        <v>375.51</v>
+      </c>
+      <c r="G526" t="n">
+        <v>373.7</v>
+      </c>
+      <c r="H526" t="n">
+        <v>374.07</v>
+      </c>
+      <c r="I526" t="n">
+        <v>373.92</v>
+      </c>
+      <c r="J526" t="n">
+        <v>368.55</v>
+      </c>
+      <c r="K526" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="L526" t="n">
+        <v>373.22</v>
+      </c>
+      <c r="M526" t="n">
+        <v>382.56</v>
+      </c>
+      <c r="N526" t="n">
+        <v>384.89</v>
+      </c>
+      <c r="O526" t="n">
+        <v>394.53</v>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>425.21</v>
+      </c>
+      <c r="C527" t="n">
+        <v>417.93</v>
+      </c>
+      <c r="D527" t="n">
+        <v>387.57</v>
+      </c>
+      <c r="E527" t="n">
+        <v>376.13</v>
+      </c>
+      <c r="F527" t="n">
+        <v>374.27</v>
+      </c>
+      <c r="G527" t="n">
+        <v>373</v>
+      </c>
+      <c r="H527" t="n">
+        <v>373.12</v>
+      </c>
+      <c r="I527" t="n">
+        <v>373.57</v>
+      </c>
+      <c r="J527" t="n">
+        <v>367.66</v>
+      </c>
+      <c r="K527" t="n">
+        <v>366.17</v>
+      </c>
+      <c r="L527" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="M527" t="n">
+        <v>381.75</v>
+      </c>
+      <c r="N527" t="n">
+        <v>383.93</v>
+      </c>
+      <c r="O527" t="n">
+        <v>394.25</v>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:18:30+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>425.21</v>
+      </c>
+      <c r="C528" t="n">
+        <v>419.41</v>
+      </c>
+      <c r="D528" t="n">
+        <v>388.48</v>
+      </c>
+      <c r="E528" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="F528" t="n">
+        <v>374.41</v>
+      </c>
+      <c r="G528" t="n">
+        <v>373.22</v>
+      </c>
+      <c r="H528" t="n">
+        <v>373.37</v>
+      </c>
+      <c r="I528" t="n">
+        <v>374.18</v>
+      </c>
+      <c r="J528" t="n">
+        <v>368.57</v>
+      </c>
+      <c r="K528" t="n">
+        <v>366.28</v>
+      </c>
+      <c r="L528" t="n">
+        <v>371.27</v>
+      </c>
+      <c r="M528" t="n">
+        <v>380.95</v>
+      </c>
+      <c r="N528" t="n">
+        <v>383.21</v>
+      </c>
+      <c r="O528" t="n">
+        <v>395.2</v>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28728,7 +28944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B549"/>
+  <dimension ref="A1:B553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34221,6 +34437,46 @@
       </c>
       <c r="B549" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>-0.96</v>
       </c>
     </row>
   </sheetData>
@@ -34389,28 +34645,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>1.468805993759896</v>
+        <v>1.443641587533086</v>
       </c>
       <c r="J2" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K2" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3247558391545859</v>
+        <v>0.3180591993785217</v>
       </c>
       <c r="M2" t="n">
-        <v>11.53362851584307</v>
+        <v>11.5824224724733</v>
       </c>
       <c r="N2" t="n">
-        <v>236.7026020884093</v>
+        <v>237.2916756489218</v>
       </c>
       <c r="O2" t="n">
-        <v>15.38514225115937</v>
+        <v>15.40427459015587</v>
       </c>
       <c r="P2" t="n">
-        <v>404.469263954954</v>
+        <v>404.7581222142078</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34467,28 +34723,28 @@
         <v>0.0436</v>
       </c>
       <c r="I3" t="n">
-        <v>1.096065877037815</v>
+        <v>1.106282282463535</v>
       </c>
       <c r="J3" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K3" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1955761230210683</v>
+        <v>0.2005103532840652</v>
       </c>
       <c r="M3" t="n">
-        <v>13.78029855756291</v>
+        <v>13.73987422759856</v>
       </c>
       <c r="N3" t="n">
-        <v>259.1406379674283</v>
+        <v>257.5590481043049</v>
       </c>
       <c r="O3" t="n">
-        <v>16.0978457554863</v>
+        <v>16.04864630130233</v>
       </c>
       <c r="P3" t="n">
-        <v>381.725429735733</v>
+        <v>381.6077539478167</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34545,28 +34801,28 @@
         <v>0.0762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1053994043676049</v>
+        <v>0.1060049337543508</v>
       </c>
       <c r="J4" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K4" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006683475088567259</v>
+        <v>0.006854670807998842</v>
       </c>
       <c r="M4" t="n">
-        <v>7.490817008110533</v>
+        <v>7.43907673970563</v>
       </c>
       <c r="N4" t="n">
-        <v>86.49254050494069</v>
+        <v>85.83882121491318</v>
       </c>
       <c r="O4" t="n">
-        <v>9.300136585284148</v>
+        <v>9.264924242265188</v>
       </c>
       <c r="P4" t="n">
-        <v>385.1098480609645</v>
+        <v>385.1028819167188</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34623,28 +34879,28 @@
         <v>0.0934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3489328501698655</v>
+        <v>-0.3540039696439654</v>
       </c>
       <c r="J5" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K5" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1046916049466662</v>
+        <v>0.10860058823819</v>
       </c>
       <c r="M5" t="n">
-        <v>5.863847695481002</v>
+        <v>5.839351581875338</v>
       </c>
       <c r="N5" t="n">
-        <v>54.50463042968068</v>
+        <v>54.18901975464561</v>
       </c>
       <c r="O5" t="n">
-        <v>7.382725135726013</v>
+        <v>7.361319158591455</v>
       </c>
       <c r="P5" t="n">
-        <v>389.8855294288611</v>
+        <v>389.9440523985263</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34701,28 +34957,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4140313310529868</v>
+        <v>-0.4198528413278349</v>
       </c>
       <c r="J6" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K6" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L6" t="n">
-        <v>0.116825806217433</v>
+        <v>0.1210205178859294</v>
       </c>
       <c r="M6" t="n">
-        <v>6.197874759012754</v>
+        <v>6.168745851390432</v>
       </c>
       <c r="N6" t="n">
-        <v>67.88768681695703</v>
+        <v>67.5024147665595</v>
       </c>
       <c r="O6" t="n">
-        <v>8.239398449945059</v>
+        <v>8.215985319276045</v>
       </c>
       <c r="P6" t="n">
-        <v>390.2790179421123</v>
+        <v>390.3460941966786</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34779,28 +35035,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4011456657121487</v>
+        <v>-0.4077802637971225</v>
       </c>
       <c r="J7" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K7" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1150291719113913</v>
+        <v>0.119616295842379</v>
       </c>
       <c r="M7" t="n">
-        <v>6.089894602748335</v>
+        <v>6.068532795464528</v>
       </c>
       <c r="N7" t="n">
-        <v>64.85480881577017</v>
+        <v>64.52669718367365</v>
       </c>
       <c r="O7" t="n">
-        <v>8.053248339382698</v>
+        <v>8.032851124206999</v>
       </c>
       <c r="P7" t="n">
-        <v>388.8959044519893</v>
+        <v>388.9723355675564</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34857,28 +35113,28 @@
         <v>0.0761</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4253012392132585</v>
+        <v>-0.4344232337170562</v>
       </c>
       <c r="J8" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K8" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L8" t="n">
-        <v>0.124325980453005</v>
+        <v>0.1300756806274729</v>
       </c>
       <c r="M8" t="n">
-        <v>6.335783641877049</v>
+        <v>6.321166811301461</v>
       </c>
       <c r="N8" t="n">
-        <v>66.74071911707598</v>
+        <v>66.54521592335733</v>
       </c>
       <c r="O8" t="n">
-        <v>8.169499318628773</v>
+        <v>8.157525110188589</v>
       </c>
       <c r="P8" t="n">
-        <v>391.5770248946562</v>
+        <v>391.6821111388196</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34935,28 +35191,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5352432990898103</v>
+        <v>-0.5437044759093527</v>
       </c>
       <c r="J9" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K9" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1752528563671242</v>
+        <v>0.1813495900968224</v>
       </c>
       <c r="M9" t="n">
-        <v>6.27502596779827</v>
+        <v>6.26233892077528</v>
       </c>
       <c r="N9" t="n">
-        <v>70.62772322269869</v>
+        <v>70.3579387035066</v>
       </c>
       <c r="O9" t="n">
-        <v>8.404030177402904</v>
+        <v>8.387963918824795</v>
       </c>
       <c r="P9" t="n">
-        <v>394.2824950850535</v>
+        <v>394.3799588123308</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35013,28 +35269,28 @@
         <v>0.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5907214214324459</v>
+        <v>-0.6023987216889377</v>
       </c>
       <c r="J10" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K10" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1847326728217941</v>
+        <v>0.1918876914968298</v>
       </c>
       <c r="M10" t="n">
-        <v>6.728320405841939</v>
+        <v>6.727789921524432</v>
       </c>
       <c r="N10" t="n">
-        <v>80.68950880496784</v>
+        <v>80.58686149518913</v>
       </c>
       <c r="O10" t="n">
-        <v>8.982733927094126</v>
+        <v>8.977018519262904</v>
       </c>
       <c r="P10" t="n">
-        <v>392.6457325916234</v>
+        <v>392.7803119988174</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35091,28 +35347,28 @@
         <v>0.0771</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6119603434402564</v>
+        <v>-0.6200627357609677</v>
       </c>
       <c r="J11" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K11" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1769614689386267</v>
+        <v>0.1824966118860467</v>
       </c>
       <c r="M11" t="n">
-        <v>7.264181675807451</v>
+        <v>7.236749835063284</v>
       </c>
       <c r="N11" t="n">
-        <v>91.24414914427389</v>
+        <v>90.80534336083763</v>
       </c>
       <c r="O11" t="n">
-        <v>9.552180334576702</v>
+        <v>9.529183772015189</v>
       </c>
       <c r="P11" t="n">
-        <v>389.3579005465226</v>
+        <v>389.4512585089282</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35169,28 +35425,28 @@
         <v>0.0854</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4686882590321776</v>
+        <v>-0.4669936018899304</v>
       </c>
       <c r="J12" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K12" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1440397801015334</v>
+        <v>0.144827304624099</v>
       </c>
       <c r="M12" t="n">
-        <v>6.534441907495265</v>
+        <v>6.498926981006634</v>
       </c>
       <c r="N12" t="n">
-        <v>68.38428241868318</v>
+        <v>67.89387935559306</v>
       </c>
       <c r="O12" t="n">
-        <v>8.269478968996969</v>
+        <v>8.239774229649321</v>
       </c>
       <c r="P12" t="n">
-        <v>384.3253834115379</v>
+        <v>384.3059027814075</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35247,28 +35503,28 @@
         <v>0.102</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07310263062386121</v>
+        <v>-0.06514906644715553</v>
       </c>
       <c r="J13" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K13" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00630962960899728</v>
+        <v>0.005058904665870001</v>
       </c>
       <c r="M13" t="n">
-        <v>5.122734376752351</v>
+        <v>5.141227155519729</v>
       </c>
       <c r="N13" t="n">
-        <v>44.39998047340697</v>
+        <v>44.3204526713287</v>
       </c>
       <c r="O13" t="n">
-        <v>6.663331034355638</v>
+        <v>6.657360788730674</v>
       </c>
       <c r="P13" t="n">
-        <v>378.8930687863089</v>
+        <v>378.8019003185728</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35325,28 +35581,28 @@
         <v>0.0586</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.006429956610919615</v>
+        <v>-0.003938840262889516</v>
       </c>
       <c r="J14" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K14" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="L14" t="n">
-        <v>4.339824983379259e-05</v>
+        <v>1.650346577297679e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>5.285101698689962</v>
+        <v>5.262303008697673</v>
       </c>
       <c r="N14" t="n">
-        <v>50.25677008450495</v>
+        <v>49.91158166091297</v>
       </c>
       <c r="O14" t="n">
-        <v>7.08920094823845</v>
+        <v>7.064812924693262</v>
       </c>
       <c r="P14" t="n">
-        <v>383.0720556392565</v>
+        <v>383.0435217084811</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35403,28 +35659,28 @@
         <v>0.0416</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.04437331575019148</v>
+        <v>-0.03884818160379998</v>
       </c>
       <c r="J15" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="K15" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003195334441806308</v>
+        <v>0.002476560317373089</v>
       </c>
       <c r="M15" t="n">
-        <v>4.492664607289538</v>
+        <v>4.487758146209705</v>
       </c>
       <c r="N15" t="n">
-        <v>32.2761236971192</v>
+        <v>32.14580273958885</v>
       </c>
       <c r="O15" t="n">
-        <v>5.681207943485187</v>
+        <v>5.669726866400961</v>
       </c>
       <c r="P15" t="n">
-        <v>392.1275292151616</v>
+        <v>392.0639481501527</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35462,7 +35718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P524"/>
+  <dimension ref="A1:P528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78357,6 +78613,334 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-40.727933795437345,172.3147433031431</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-40.72748056062553,172.31542211275908</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-40.72714120341095,172.31626903437274</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-40.72669670509385,172.31696075411844</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-40.72620177802403,172.31756788493135</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-40.72568792910943,172.3181462694151</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-40.72515342593885,172.31870194989168</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-40.72462220002327,172.31926372866332</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>-40.72411740008404,172.31986613043136</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>-40.723582962109184,172.32041998423335</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>-40.72300953713356,172.32091080774399</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>-40.72241746056781,172.32137029460532</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>-40.72185747102345,172.32192014262498</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>-40.721304097880456,172.3224781046194</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:18:41+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-40.72794499808809,172.31475984027637</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-40.72748056062553,172.31542211275908</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-40.72714743367379,172.31627823149296</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-40.726702575882,172.31696942062237</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-40.72620609538418,172.31757456127616</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-40.72568991103861,172.31814949256798</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-40.72515596862451,172.31870609975527</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-40.7246246861918,172.3192677862899</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-40.72412378285322,172.31987670493706</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>-40.72359194716833,172.32043509920948</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>-40.72302212536889,172.32093198918537</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>-40.722431934207926,172.3213946484449</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>-40.72186806525884,172.32193612043483</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>-40.721309810903065,172.32248583161584</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-40.72794637595407,172.3147618742557</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-40.72747954220878,172.31542060938625</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-40.727150968149516,172.31628344909078</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-40.726709045729415,172.3169789714652</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-40.72621332987872,172.31758574866674</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-40.72569387489669,172.31815593887427</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-40.72516133651598,172.31871486057943</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-40.72462666382578,172.31927101394763</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-40.72412876589165,172.3198849604736</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>-40.723599601106066,172.3204479749331</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>-40.72302844721249,172.32094262656423</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>-40.72243642602624,172.32140220653523</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>-40.7218737470825,172.32194468954162</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>-40.72131156875609,172.32248820915348</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:18:30+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-40.72794637595407,172.3147618742557</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-40.72747067599155,172.31540752120148</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-40.72714551666993,172.31627540160966</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-40.72670724854966,172.31697631845313</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-40.72621251308101,172.31758448557414</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-40.725692629112764,172.3181539128922</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-40.72515992391303,172.31871255509927</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-40.72462321709223,172.31926538860142</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-40.724123670874825,172.31987651941938</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>-40.72359899100963,172.32044694860718</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>-40.723032939048146,172.3209501847031</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>-40.72244086238952,172.32140967131673</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>-40.72187800844982,172.32195111637267</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>-40.72130560461174,172.32248014250845</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0317/nzd0317.xlsx
+++ b/data/nzd0317/nzd0317.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P528"/>
+  <dimension ref="A1:P532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28886,7 +28886,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>425.21</v>
+        <v>430.68</v>
       </c>
       <c r="C528" t="n">
         <v>419.41</v>
@@ -28928,6 +28928,222 @@
         <v>395.2</v>
       </c>
       <c r="P528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>430.68</v>
+      </c>
+      <c r="C529" t="n">
+        <v>419.41</v>
+      </c>
+      <c r="D529" t="n">
+        <v>388.48</v>
+      </c>
+      <c r="E529" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="F529" t="n">
+        <v>374.41</v>
+      </c>
+      <c r="G529" t="n">
+        <v>373.22</v>
+      </c>
+      <c r="H529" t="n">
+        <v>373.66</v>
+      </c>
+      <c r="I529" t="n">
+        <v>374.53</v>
+      </c>
+      <c r="J529" t="n">
+        <v>369.35</v>
+      </c>
+      <c r="K529" t="n">
+        <v>366.35</v>
+      </c>
+      <c r="L529" t="n">
+        <v>370.54</v>
+      </c>
+      <c r="M529" t="n">
+        <v>380.03</v>
+      </c>
+      <c r="N529" t="n">
+        <v>382.41</v>
+      </c>
+      <c r="O529" t="n">
+        <v>393.99</v>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>435.09</v>
+      </c>
+      <c r="C530" t="n">
+        <v>422.33</v>
+      </c>
+      <c r="D530" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="E530" t="n">
+        <v>376.96</v>
+      </c>
+      <c r="F530" t="n">
+        <v>375.39</v>
+      </c>
+      <c r="G530" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="H530" t="n">
+        <v>374.01</v>
+      </c>
+      <c r="I530" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="J530" t="n">
+        <v>370.41</v>
+      </c>
+      <c r="K530" t="n">
+        <v>366.13</v>
+      </c>
+      <c r="L530" t="n">
+        <v>368.92</v>
+      </c>
+      <c r="M530" t="n">
+        <v>378.1</v>
+      </c>
+      <c r="N530" t="n">
+        <v>380.44</v>
+      </c>
+      <c r="O530" t="n">
+        <v>394.77</v>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>435.09</v>
+      </c>
+      <c r="C531" t="n">
+        <v>422.33</v>
+      </c>
+      <c r="D531" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="E531" t="n">
+        <v>376.96</v>
+      </c>
+      <c r="F531" t="n">
+        <v>375.39</v>
+      </c>
+      <c r="G531" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="H531" t="n">
+        <v>374.1</v>
+      </c>
+      <c r="I531" t="n">
+        <v>375.53</v>
+      </c>
+      <c r="J531" t="n">
+        <v>371.03</v>
+      </c>
+      <c r="K531" t="n">
+        <v>366.16</v>
+      </c>
+      <c r="L531" t="n">
+        <v>368.07</v>
+      </c>
+      <c r="M531" t="n">
+        <v>377.34</v>
+      </c>
+      <c r="N531" t="n">
+        <v>379.44</v>
+      </c>
+      <c r="O531" t="n">
+        <v>394.64</v>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>435.09</v>
+      </c>
+      <c r="C532" t="n">
+        <v>422.33</v>
+      </c>
+      <c r="D532" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="E532" t="n">
+        <v>376.96</v>
+      </c>
+      <c r="F532" t="n">
+        <v>375.39</v>
+      </c>
+      <c r="G532" t="n">
+        <v>374.2</v>
+      </c>
+      <c r="H532" t="n">
+        <v>374.5</v>
+      </c>
+      <c r="I532" t="n">
+        <v>375.97</v>
+      </c>
+      <c r="J532" t="n">
+        <v>371.41</v>
+      </c>
+      <c r="K532" t="n">
+        <v>366.53</v>
+      </c>
+      <c r="L532" t="n">
+        <v>367.83</v>
+      </c>
+      <c r="M532" t="n">
+        <v>377.05</v>
+      </c>
+      <c r="N532" t="n">
+        <v>379.33</v>
+      </c>
+      <c r="O532" t="n">
+        <v>394.13</v>
+      </c>
+      <c r="P532" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28944,7 +29160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B553"/>
+  <dimension ref="A1:B557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34477,6 +34693,46 @@
       </c>
       <c r="B553" t="n">
         <v>-0.96</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -34645,28 +34901,28 @@
         <v>0.0302</v>
       </c>
       <c r="I2" t="n">
-        <v>1.443641587533086</v>
+        <v>1.432441585582224</v>
       </c>
       <c r="J2" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K2" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3180591993785217</v>
+        <v>0.3173375724680507</v>
       </c>
       <c r="M2" t="n">
-        <v>11.5824224724733</v>
+        <v>11.55729758907159</v>
       </c>
       <c r="N2" t="n">
-        <v>237.2916756489218</v>
+        <v>235.8679228493305</v>
       </c>
       <c r="O2" t="n">
-        <v>15.40427459015587</v>
+        <v>15.35799214901904</v>
       </c>
       <c r="P2" t="n">
-        <v>404.7581222142078</v>
+        <v>404.8871958862617</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34723,28 +34979,28 @@
         <v>0.0436</v>
       </c>
       <c r="I3" t="n">
-        <v>1.106282282463535</v>
+        <v>1.120744039259919</v>
       </c>
       <c r="J3" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K3" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2005103532840652</v>
+        <v>0.2064569505109093</v>
       </c>
       <c r="M3" t="n">
-        <v>13.73987422759856</v>
+        <v>13.72608808318345</v>
       </c>
       <c r="N3" t="n">
-        <v>257.5590481043049</v>
+        <v>256.4182052182044</v>
       </c>
       <c r="O3" t="n">
-        <v>16.04864630130233</v>
+        <v>16.01306358003379</v>
       </c>
       <c r="P3" t="n">
-        <v>381.6077539478167</v>
+        <v>381.4405230397411</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34801,28 +35057,28 @@
         <v>0.0762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1060049337543508</v>
+        <v>0.1075486969895723</v>
       </c>
       <c r="J4" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K4" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006854670807998842</v>
+        <v>0.007151439876577292</v>
       </c>
       <c r="M4" t="n">
-        <v>7.43907673970563</v>
+        <v>7.392632193469288</v>
       </c>
       <c r="N4" t="n">
-        <v>85.83882121491318</v>
+        <v>85.20082064172816</v>
       </c>
       <c r="O4" t="n">
-        <v>9.264924242265188</v>
+        <v>9.230429060543619</v>
       </c>
       <c r="P4" t="n">
-        <v>385.1028819167188</v>
+        <v>385.085024805274</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34879,28 +35135,28 @@
         <v>0.0934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3540039696439654</v>
+        <v>-0.3590822767367497</v>
       </c>
       <c r="J5" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K5" t="n">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="L5" t="n">
-        <v>0.10860058823819</v>
+        <v>0.1125856706195791</v>
       </c>
       <c r="M5" t="n">
-        <v>5.839351581875338</v>
+        <v>5.815234832383202</v>
       </c>
       <c r="N5" t="n">
-        <v>54.18901975464561</v>
+        <v>53.87691363794078</v>
       </c>
       <c r="O5" t="n">
-        <v>7.361319158591455</v>
+        <v>7.340089484327884</v>
       </c>
       <c r="P5" t="n">
-        <v>389.9440523985263</v>
+        <v>390.0028653151832</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34957,28 +35213,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4198528413278349</v>
+        <v>-0.42537143753231</v>
       </c>
       <c r="J6" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K6" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1210205178859294</v>
+        <v>0.1251489333241578</v>
       </c>
       <c r="M6" t="n">
-        <v>6.168745851390432</v>
+        <v>6.139275045388986</v>
       </c>
       <c r="N6" t="n">
-        <v>67.5024147665595</v>
+        <v>67.11005216758385</v>
       </c>
       <c r="O6" t="n">
-        <v>8.215985319276045</v>
+        <v>8.192072519673141</v>
       </c>
       <c r="P6" t="n">
-        <v>390.3460941966786</v>
+        <v>390.4099024051972</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35035,28 +35291,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4077802637971225</v>
+        <v>-0.4137706849891946</v>
       </c>
       <c r="J7" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K7" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="L7" t="n">
-        <v>0.119616295842379</v>
+        <v>0.1239916955358285</v>
       </c>
       <c r="M7" t="n">
-        <v>6.068532795464528</v>
+        <v>6.045031668543082</v>
       </c>
       <c r="N7" t="n">
-        <v>64.52669718367365</v>
+        <v>64.17694125944367</v>
       </c>
       <c r="O7" t="n">
-        <v>8.032851124206999</v>
+        <v>8.011051195657387</v>
       </c>
       <c r="P7" t="n">
-        <v>388.9723355675564</v>
+        <v>389.0416006102508</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35113,28 +35369,28 @@
         <v>0.0761</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4344232337170562</v>
+        <v>-0.4427653371697167</v>
       </c>
       <c r="J8" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K8" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1300756806274729</v>
+        <v>0.1355948410654649</v>
       </c>
       <c r="M8" t="n">
-        <v>6.321166811301461</v>
+        <v>6.303980499415703</v>
       </c>
       <c r="N8" t="n">
-        <v>66.54521592335733</v>
+        <v>66.30791388473335</v>
       </c>
       <c r="O8" t="n">
-        <v>8.157525110188589</v>
+        <v>8.142967142555184</v>
       </c>
       <c r="P8" t="n">
-        <v>391.6821111388196</v>
+        <v>391.7785714671452</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35191,28 +35447,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5437044759093527</v>
+        <v>-0.5500224243935191</v>
       </c>
       <c r="J9" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K9" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1813495900968224</v>
+        <v>0.1865715768620461</v>
       </c>
       <c r="M9" t="n">
-        <v>6.26233892077528</v>
+        <v>6.240773641116788</v>
       </c>
       <c r="N9" t="n">
-        <v>70.3579387035066</v>
+        <v>69.98075228918123</v>
       </c>
       <c r="O9" t="n">
-        <v>8.387963918824795</v>
+        <v>8.365449915526435</v>
       </c>
       <c r="P9" t="n">
-        <v>394.3799588123308</v>
+        <v>394.453008259065</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35269,28 +35525,28 @@
         <v>0.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6023987216889377</v>
+        <v>-0.6109043943742475</v>
       </c>
       <c r="J10" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K10" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1918876914968298</v>
+        <v>0.1979155402175182</v>
       </c>
       <c r="M10" t="n">
-        <v>6.727789921524432</v>
+        <v>6.713434359581981</v>
       </c>
       <c r="N10" t="n">
-        <v>80.58686149518913</v>
+        <v>80.25736770750459</v>
       </c>
       <c r="O10" t="n">
-        <v>8.977018519262904</v>
+        <v>8.958647649478385</v>
       </c>
       <c r="P10" t="n">
-        <v>392.7803119988174</v>
+        <v>392.8786999628633</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35347,28 +35603,28 @@
         <v>0.0771</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6200627357609677</v>
+        <v>-0.6292050642655875</v>
       </c>
       <c r="J11" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K11" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1824966118860467</v>
+        <v>0.1884848653858274</v>
       </c>
       <c r="M11" t="n">
-        <v>7.236749835063284</v>
+        <v>7.21319846252411</v>
       </c>
       <c r="N11" t="n">
-        <v>90.80534336083763</v>
+        <v>90.43749244186213</v>
       </c>
       <c r="O11" t="n">
-        <v>9.529183772015189</v>
+        <v>9.509862903420959</v>
       </c>
       <c r="P11" t="n">
-        <v>389.4512585089282</v>
+        <v>389.5569769816722</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35425,28 +35681,28 @@
         <v>0.0854</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4669936018899304</v>
+        <v>-0.4711234920689596</v>
       </c>
       <c r="J12" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K12" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="L12" t="n">
-        <v>0.144827304624099</v>
+        <v>0.1486342888743488</v>
       </c>
       <c r="M12" t="n">
-        <v>6.498926981006634</v>
+        <v>6.464429669911893</v>
       </c>
       <c r="N12" t="n">
-        <v>67.89387935559306</v>
+        <v>67.45445214366733</v>
       </c>
       <c r="O12" t="n">
-        <v>8.239774229649321</v>
+        <v>8.213065940540556</v>
       </c>
       <c r="P12" t="n">
-        <v>384.3059027814075</v>
+        <v>384.3536781310154</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35503,28 +35759,28 @@
         <v>0.102</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06514906644715553</v>
+        <v>-0.0636648735958955</v>
       </c>
       <c r="J13" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K13" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005058904665870001</v>
+        <v>0.004897092698946337</v>
       </c>
       <c r="M13" t="n">
-        <v>5.141227155519729</v>
+        <v>5.113247113566283</v>
       </c>
       <c r="N13" t="n">
-        <v>44.3204526713287</v>
+        <v>44.00521390258</v>
       </c>
       <c r="O13" t="n">
-        <v>6.657360788730674</v>
+        <v>6.633642581763054</v>
       </c>
       <c r="P13" t="n">
-        <v>378.8019003185728</v>
+        <v>378.7848339198314</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35581,28 +35837,28 @@
         <v>0.0586</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.003938840262889516</v>
+        <v>-0.007457131582466557</v>
       </c>
       <c r="J14" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K14" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="L14" t="n">
-        <v>1.650346577297679e-05</v>
+        <v>5.990446828563201e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>5.262303008697673</v>
+        <v>5.23601796062772</v>
       </c>
       <c r="N14" t="n">
-        <v>49.91158166091297</v>
+        <v>49.59445043152366</v>
       </c>
       <c r="O14" t="n">
-        <v>7.064812924693262</v>
+        <v>7.042332740755982</v>
       </c>
       <c r="P14" t="n">
-        <v>383.0435217084811</v>
+        <v>383.0840474932327</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35659,28 +35915,28 @@
         <v>0.0416</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.03884818160379998</v>
+        <v>-0.03416428071723326</v>
       </c>
       <c r="J15" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="K15" t="n">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002476560317373089</v>
+        <v>0.001938008556003568</v>
       </c>
       <c r="M15" t="n">
-        <v>4.487758146209705</v>
+        <v>4.478764676728012</v>
       </c>
       <c r="N15" t="n">
-        <v>32.14580273958885</v>
+        <v>31.98676708704736</v>
       </c>
       <c r="O15" t="n">
-        <v>5.669726866400961</v>
+        <v>5.655684493237522</v>
       </c>
       <c r="P15" t="n">
-        <v>392.0639481501527</v>
+        <v>392.0098304830295</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35718,7 +35974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P528"/>
+  <dimension ref="A1:P532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78867,7 +79123,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>-40.72794637595407,172.3147618742557</t>
+          <t>-40.727913606697136,172.31471350094375</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -78936,6 +79192,334 @@
         </is>
       </c>
       <c r="P528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-40.727913606697136,172.31471350094375</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-40.72747067599155,172.31540752120148</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-40.72714551666993,172.31627540160966</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-40.72670724854966,172.31697631845313</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-40.72621251308101,172.31758448557414</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-40.725692629112764,172.3181539128922</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-40.72515828529353,172.31870988074238</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-40.72462123945812,172.31926216094402</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>-40.72411930371705,172.3198692842311</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>-40.72359860276644,172.3204462954907</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>-40.72303698724529,172.32095699635997</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>-40.722445964206706,172.32141825581675</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>-40.721882743302004,172.32195825729704</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>-40.72131320104815,172.3224904168671</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-40.72788718759238,172.31467450165374</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-40.727453183180245,172.31538169857683</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>-40.72714096378543,172.3162686806374</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-40.72670407353193,172.31697163146546</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>-40.7262067954966,172.31757564392677</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-40.72568934477314,172.31814857166714</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>-40.72515630764925,172.31870665307042</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>-40.72461790573182,172.3192567200363</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>-40.724113368860905,172.31985945179724</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>-40.723599822959315,172.32044834814252</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>-40.72304597091424,172.32097211264255</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>-40.72245666692983,172.3214362646091</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>-40.72189440287362,172.32197584182762</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>-40.721308304171885,172.32248379372655</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-40.72788718759238,172.31467450165374</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-40.727453183180245,172.31538169857683</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-40.72714096378543,172.3162686806374</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-40.72670407353193,172.31697163146546</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-40.7262067954966,172.31757564392677</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-40.72568934477314,172.31814857166714</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>-40.725155799112144,172.3187058230977</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>-40.724615589074425,172.3192529390668</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>-40.72410989752957,172.31985370075182</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>-40.72359965656936,172.32044806823546</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>-40.72305068456692,172.320980044027</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>-40.72246088147288,172.32144335615584</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>-40.72190032143688,172.32198476798763</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>-40.72130912031795,172.32248489758322</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-40.72788718759238,172.31467450165374</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-40.727453183180245,172.31538169857683</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-40.72714096378543,172.3162686806374</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-40.72670407353193,172.31697163146546</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-40.7262067954966,172.31757564392677</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-40.72568707971119,172.31814488806396</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>-40.72515353894711,172.31870213433007</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>-40.724613102905366,172.31924888144133</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>-40.72410776993926,172.31985017591785</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>-40.723597604426786,172.32044461604838</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>-40.72305201548052,172.32098228347695</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>-40.72246248965367,172.32144606214104</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>-40.7219009724788,172.32198574986535</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>-40.721312322121655,172.3224892280982</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
